--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vokabeln" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fortschritt" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Vokabeln" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fortschritt" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L85"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5415,6 +5415,62 @@
       <c r="L85" s="5" t="inlineStr">
         <is>
           <t>Kitchen/Cooking</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>napkin</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Serviette</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>/ˈnæpkɪn/</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>A piece of cloth or paper used to wipe mouth and hands while eating.</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>She wiped her mouth with a napkin after dinner.</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Please put a napkin on your lap before eating.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Brede-LilleBrede-napkin.jpg?width=400</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
         </is>
       </c>
     </row>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L86"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5467,8 +5467,59 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>to struggle</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>kämpfen</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>/ˈstrʌɡəl/</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>To try very hard to do something difficult or to deal with a problem.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>She struggled to open the heavy door.</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Many students struggle with mathematics.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5509,7 +5509,6 @@
           <t>Many students struggle with mathematics.</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
         <v>2</v>
       </c>
@@ -5518,8 +5517,63 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Democracy</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Demokratie</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>/dɪˈmɒkrəsi/</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>A system of government where citizens choose leaders through voting.</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Democracy gives people the right to vote.</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Many countries practice democracy today.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Urne_Ballot_box_république.jpg?width=400</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>2</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5572,8 +5572,59 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>furious</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>wütend</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>/ˈfjʊəriəs/</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Extremely angry or full of rage.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>She was furious when she discovered the broken window.</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>The coach became furious after the team lost the game.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="n">
+        <v>2</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L89"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5614,7 +5614,6 @@
           <t>The coach became furious after the team lost the game.</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
         <v>2</v>
       </c>
@@ -5623,8 +5622,59 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>to blackmail</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>erpressen</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>/ˈblækmeɪl/</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>To demand money or favors by threatening to reveal compromising information about someone.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>He tried to blackmail her with old photographs.</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>The criminal blackmailed the businessman for thousands of dollars.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="n">
+        <v>2</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5664,7 +5664,6 @@
           <t>The criminal blackmailed the businessman for thousands of dollars.</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
         <v>2</v>
       </c>
@@ -5673,8 +5672,59 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>infatuated</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>vernarrt</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>/ɪnˈfætʃueɪtɪd/</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Possessed with an intense but short-lived passion or admiration for someone</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>She became infatuated with her new colleague.</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>He was infatuated with the idea of becoming famous.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="n">
+        <v>2</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5714,7 +5714,6 @@
           <t>He was infatuated with the idea of becoming famous.</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
         <v>2</v>
       </c>
@@ -5723,8 +5722,59 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>abstinent</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>enthaltsam</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>/ˈæbstɪnənt/</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Practicing self-restraint, especially from alcohol or certain foods.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>He has been abstinent from alcohol for two years.</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>She follows an abstinent lifestyle for health reasons.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="n">
+        <v>3</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5764,7 +5764,6 @@
           <t>She follows an abstinent lifestyle for health reasons.</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="n">
         <v>3</v>
       </c>
@@ -5773,8 +5772,59 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>persistent</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>beharrlich, ausdauernd</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>/pəˈsɪstənt/</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Continuing firmly despite difficulty or opposition</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>She was persistent in her efforts to learn English.</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>The persistent rain lasted for three days.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="n">
+        <v>2</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5814,7 +5814,6 @@
           <t>The persistent rain lasted for three days.</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
         <v>2</v>
       </c>
@@ -5823,8 +5822,59 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>to steep tea</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Tee ziehen lassen</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>/tuː stiːp tiː/</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Phrase</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>To let tea leaves sit in hot water to release flavor and color.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>You should steep tea for about three to five minutes.</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>She steeped the tea in boiling water before serving it.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="n">
+        <v>2</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5864,7 +5864,6 @@
           <t>She steeped the tea in boiling water before serving it.</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
         <v>2</v>
       </c>
@@ -5873,8 +5872,59 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Personally Identifiable Information (PII)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>personenbezogene Daten</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>/ˈpɜːrsənəli aɪˈdentɪfaɪəbl ˌɪnfərˈmeɪʃən/</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Phrase</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Data that can identify a specific individual, such as name, address, or social security number.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Companies must protect PII to comply with privacy regulations.</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Never share your PII with untrusted websites or emails.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="n">
+        <v>3</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5914,7 +5914,6 @@
           <t>Never share your PII with untrusted websites or emails.</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
         <v>3</v>
       </c>
@@ -5923,8 +5922,59 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>pointless</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>sinnlos</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>/ˈpɔɪntləs/</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Having no purpose, use, or likelihood of success.</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>It's pointless to argue about it now.</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>The meeting was completely pointless.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="n">
+        <v>2</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5964,7 +5964,6 @@
           <t>The meeting was completely pointless.</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
         <v>2</v>
       </c>
@@ -5973,8 +5972,59 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>cheerful</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>fröhlich</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>/ˈtʃɪəfəl/</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Noticeably happy and optimistic in mood or manner.</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>She greeted us with a cheerful smile.</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>The children were cheerful despite the rain.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="n">
+        <v>2</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6014,7 +6014,6 @@
           <t>The children were cheerful despite the rain.</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
         <v>2</v>
       </c>
@@ -6023,8 +6022,59 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>clumsy</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ungeschickt</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>/ˈklʌmzi/</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Moving or doing things in an awkward way, often causing accidents or mistakes.</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>He is too clumsy to carry those fragile dishes.</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>She made a clumsy attempt to catch the ball.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="n">
+        <v>2</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6064,7 +6064,6 @@
           <t>She made a clumsy attempt to catch the ball.</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
         <v>2</v>
       </c>
@@ -6073,8 +6072,63 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>exploitation</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Ausbeutung</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>/ˌeksplɔɪˈteɪʃən/</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>The action of treating someone unfairly to benefit from their work or resources.</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>The exploitation of workers in factories was common during the industrial revolution.</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Environmental exploitation leads to the destruction of natural habitats.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Continental_AG_tire_factory_Mittellandkanal_Stoecken_Hannover_Germany_02.jpg?width=400</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>3</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6127,8 +6127,59 @@
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>invocable</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>aufrufbar</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>/ɪnˈvoʊkəbl/</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Capable of being called upon or summoned, especially in programming or legal contexts.</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>The function is invocable from any part of the code.</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>This right is invocable by any citizen under the law.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="n">
+        <v>3</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6169,7 +6169,6 @@
           <t>This right is invocable by any citizen under the law.</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
         <v>3</v>
       </c>
@@ -6178,8 +6177,63 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Pitfall</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Falle, Fallstrick</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>/ˈpɪtfɔːl/</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>A hidden or unexpected danger or difficulty.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>One pitfall of online shopping is hidden delivery costs.</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Avoid the common pitfall of studying only the night before exams.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Insect_trap_hidden_in_a_tree_trunk_in_Junkerdalsura.jpg?width=400</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>2</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6232,8 +6232,59 @@
           <t>2026-05-10</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>effortless</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>mühelos</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>/ˈefətləs/</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Requiring no physical or mental effort; done with ease.</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>She made the difficult task look effortless.</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>His effortless style impressed everyone at the party.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="n">
+        <v>2</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6274,7 +6274,6 @@
           <t>His effortless style impressed everyone at the party.</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="n">
         <v>2</v>
       </c>
@@ -6283,8 +6282,59 @@
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>to stack</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>stapeln</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>/stæk/</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>To arrange things in a neat pile, one on top of another.</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Please stack the chairs after the meeting.</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>She stacked the books on the shelf.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6324,7 +6324,6 @@
           <t>She stacked the books on the shelf.</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="n">
         <v>1</v>
       </c>
@@ -6333,8 +6332,59 @@
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>to sift</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>sieben</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>/sɪft/</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>To pass a substance through a sieve to remove lumps or separate particles.</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>She sifted the flour before making the cake.</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>They sifted through the evidence to find clues.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="n">
+        <v>2</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6374,7 +6374,6 @@
           <t>They sifted through the evidence to find clues.</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
         <v>2</v>
       </c>
@@ -6383,8 +6382,59 @@
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>to dissolve</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>auflösen</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>/dɪˈzɒlv/</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>To become or cause to become incorporated into a liquid so as to form a solution.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Sugar dissolves quickly in hot water.</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>The tablet will dissolve in your mouth.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="n">
+        <v>2</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6424,7 +6424,6 @@
           <t>The tablet will dissolve in your mouth.</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="n">
         <v>2</v>
       </c>
@@ -6433,8 +6432,59 @@
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>red tape</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Bürokratie</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>/red teɪp/</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Phrase</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Excessive bureaucracy or adherence to rules and formalities, especially in public business.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>The company struggled with red tape when applying for permits.</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>We need to cut through the red tape to get this approved quickly.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="n">
+        <v>2</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -702,7 +702,11 @@
           <t>She stood at the threshold of the doorway, hesitating before stepping inside.</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Funchal_(Madeira,_Portugal),_Rua_de_Santa_Maria_1_--_2025_--_0818.jpg?width=400</t>
+        </is>
+      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
           <t>B2</t>
@@ -6474,7 +6478,6 @@
           <t>We need to cut through the red tape to get this approved quickly.</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="n">
         <v>2</v>
       </c>
@@ -6483,7 +6486,6 @@
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
           <t>Allgemein</t>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -2626,7 +2626,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Lefse_rolling_pin.jpg?width=400</t>
+          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Bagarstugan_2013-07-09_01.jpg?width=400</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6487,6 +6487,58 @@
         </is>
       </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>distorted</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>verzerrt</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>/dɪˈstɔːtɪd/</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Changed from the original shape, sound, or meaning in an unusual way.</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>The mirror showed a distorted reflection of my face.</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>The audio was distorted and hard to understand.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="n">
+        <v>2</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:L108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6528,7 +6528,6 @@
           <t>The audio was distorted and hard to understand.</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="n">
         <v>2</v>
       </c>
@@ -6537,8 +6536,63 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Beibehaltung</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>/rɪˈtenʃən/</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>The continued possession, use, or control of something.</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Customer retention is crucial for business success.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>The company improved employee retention through better benefits.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Mercy_Health_Partners_of_Southwest_Ohio_senior_health_and_housing_services_recruitment_and_retention_(R_&amp;_R)_initiative_-_DPLA_-_b80e071d7a1f9ae003c0c81c7ceacd77.jpg?width=400</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>2</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6591,8 +6591,59 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>pensive</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>nachdenklich</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>/ˈpensɪv/</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Engaged in deep or serious thought, often with a hint of sadness.</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>She had a pensive look on her face.</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>He sat pensive by the window, thinking about his future.</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="n">
+        <v>2</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6633,7 +6633,6 @@
           <t>He sat pensive by the window, thinking about his future.</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="n">
         <v>2</v>
       </c>
@@ -6642,10 +6641,61 @@
           <t>2026-05-24</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
           <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>blunt</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>stumpf, direkt</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>/blʌnt/</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Not sharp or pointed; saying what you think without trying to be polite.</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>The knife was too blunt to cut the bread.</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>She was very blunt and told him the truth.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="n">
+        <v>2</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>TV</t>
         </is>
       </c>
     </row>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -5068,7 +5068,11 @@
           <t>The tablecloth is covered in wine stains — it needs a good wash.</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr"/>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Table-cloth_2008-1.jpg?width=400</t>
+        </is>
+      </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
           <t>A2</t>
@@ -6683,7 +6687,6 @@
           <t>She was very blunt and told him the truth.</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="n">
         <v>2</v>
       </c>
@@ -6692,7 +6695,6 @@
           <t>2026-05-24</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
           <t>TV</t>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -3044,7 +3044,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Making_Mmnce_pies_-_tarts_in_baking_tray.jpg?width=400</t>
+          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Illuminated_facade_of_a_restaurant_serving_traditional_food_with_fresh_vegetables_in_Chiyoda,_Tokyo.jpg?width=400</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Vokabeln" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Fortschritt" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vokabeln" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fortschritt" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:L185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -702,11 +702,7 @@
           <t>She stood at the threshold of the doorway, hesitating before stepping inside.</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Funchal_(Madeira,_Portugal),_Rua_de_Santa_Maria_1_--_2025_--_0818.jpg?width=400</t>
-        </is>
-      </c>
+      <c r="H4" s="3" t="inlineStr"/>
       <c r="I4" s="3" t="inlineStr">
         <is>
           <t>B2</t>
@@ -2626,7 +2622,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Bagarstugan_2013-07-09_01.jpg?width=400</t>
+          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Lefse_rolling_pin.jpg?width=400</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -3044,7 +3040,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Illuminated_facade_of_a_restaurant_serving_traditional_food_with_fresh_vegetables_in_Chiyoda,_Tokyo.jpg?width=400</t>
+          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Making_Mmnce_pies_-_tarts_in_baking_tray.jpg?width=400</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -5068,11 +5064,7 @@
           <t>The tablecloth is covered in wine stains — it needs a good wash.</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Table-cloth_2008-1.jpg?width=400</t>
-        </is>
-      </c>
+      <c r="H79" s="5" t="inlineStr"/>
       <c r="I79" s="5" t="inlineStr">
         <is>
           <t>A2</t>
@@ -5429,52 +5421,51 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>napkin</t>
+          <t>significant</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Serviette</t>
+          <t>bedeutsam, wesentlich</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>/ˈnæpkɪn/</t>
+          <t>/sɪɡˈnɪfɪkənt/</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Nomen</t>
+          <t>Adjektiv</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>A piece of cloth or paper used to wipe mouth and hands while eating.</t>
+          <t>Important or large enough to have a noticeable effect.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>She wiped her mouth with a napkin after dinner.</t>
+          <t>The new policy had a significant impact on employee satisfaction.</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Please put a napkin on your lap before eating.</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Brede-LilleBrede-napkin.jpg?width=400</t>
-        </is>
-      </c>
-      <c r="I86" t="n">
-        <v>1</v>
+          <t>There is a significant difference between the two proposals.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5484,47 +5475,51 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>to struggle</t>
+          <t>subtle</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>kämpfen</t>
+          <t>subtil, fein, kaum merklich</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>/ˈstrʌɡəl/</t>
+          <t>/ˈsʌtl/</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>Adjektiv</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>To try very hard to do something difficult or to deal with a problem.</t>
+          <t>Not immediately obvious or easy to notice; delicate and understated.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>She struggled to open the heavy door.</t>
+          <t>There was a subtle change in her tone that made everyone pay attention.</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Many students struggle with mathematics.</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
-        <v>2</v>
+          <t>He made a subtle hint that he wanted to leave early.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5534,52 +5529,51 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Democracy</t>
+          <t>genuine</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Demokratie</t>
+          <t>echt, aufrichtig, authentisch</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>/dɪˈmɒkrəsi/</t>
+          <t>/ˈdʒenjuɪn/</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Nomen</t>
+          <t>Adjektiv</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>A system of government where citizens choose leaders through voting.</t>
+          <t>Truly what it appears to be; sincere and honest.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Democracy gives people the right to vote.</t>
+          <t>Her smile was genuine – she was truly happy to see him.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Many countries practice democracy today.</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Urne_Ballot_box_république.jpg?width=400</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
-        <v>2</v>
+          <t>He showed a genuine interest in learning the language.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5589,17 +5583,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>furious</t>
+          <t>remarkable</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>wütend</t>
+          <t>bemerkenswert, außergewöhnlich</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>/ˈfjʊəriəs/</t>
+          <t>/rɪˈmɑːkəbl/</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5609,27 +5603,31 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Extremely angry or full of rage.</t>
+          <t>Worthy of attention; striking or extraordinary.</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>She was furious when she discovered the broken window.</t>
+          <t>She made a remarkable recovery after the surgery.</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>The coach became furious after the team lost the game.</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>2</v>
+          <t>The film's special effects were absolutely remarkable.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5639,47 +5637,51 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>to blackmail</t>
+          <t>considerate</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>erpressen</t>
+          <t>rücksichtsvoll, aufmerksam</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>/ˈblækmeɪl/</t>
+          <t>/kənˈsɪdərɪt/</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>Adjektiv</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>To demand money or favors by threatening to reveal compromising information about someone.</t>
+          <t>Careful not to cause inconvenience or hurt to others; thoughtful.</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>He tried to blackmail her with old photographs.</t>
+          <t>He is always considerate of his neighbours and keeps the noise down.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>The criminal blackmailed the businessman for thousands of dollars.</t>
-        </is>
-      </c>
-      <c r="I90" t="n">
-        <v>2</v>
+          <t>It was considerate of her to send a thank-you note.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5689,17 +5691,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>infatuated</t>
+          <t>persistent</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>vernarrt</t>
+          <t>beharrlich, hartnäckig, anhaltend</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>/ɪnˈfætʃueɪtɪd/</t>
+          <t>/pəˈsɪstənt/</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5709,27 +5711,31 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Possessed with an intense but short-lived passion or admiration for someone</t>
+          <t>Continuing firmly despite difficulty or opposition; refusing to give up.</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>She became infatuated with her new colleague.</t>
+          <t>Despite many rejections, she remained persistent and finally got the job.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>He was infatuated with the idea of becoming famous.</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
-        <v>2</v>
+          <t>The persistent rain ruined our picnic plans.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5739,17 +5745,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>abstinent</t>
+          <t>anxious</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>enthaltsam</t>
+          <t>ängstlich, besorgt, nervös</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>/ˈæbstɪnənt/</t>
+          <t>/ˈæŋkʃəs/</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5759,27 +5765,31 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Practicing self-restraint, especially from alcohol or certain foods.</t>
+          <t>Feeling worried, uneasy, or nervous about a situation.</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>He has been abstinent from alcohol for two years.</t>
+          <t>He was anxious about the exam results and couldn't sleep.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>She follows an abstinent lifestyle for health reasons.</t>
-        </is>
-      </c>
-      <c r="I92" t="n">
-        <v>3</v>
+          <t>She felt anxious waiting for the doctor's call.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5789,17 +5799,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>persistent</t>
+          <t>exhausted</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>beharrlich, ausdauernd</t>
+          <t>erschöpft, ausgelaugt</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>/pəˈsɪstənt/</t>
+          <t>/ɪɡˈzɔːstɪd/</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5809,27 +5819,31 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Continuing firmly despite difficulty or opposition</t>
+          <t>Extremely tired; drained of physical or mental energy.</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>She was persistent in her efforts to learn English.</t>
+          <t>After the marathon, she was completely exhausted and fell asleep instantly.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>The persistent rain lasted for three days.</t>
-        </is>
-      </c>
-      <c r="I93" t="n">
-        <v>2</v>
+          <t>He looked exhausted after working three back-to-back night shifts.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5839,47 +5853,51 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>to steep tea</t>
+          <t>frustrated</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tee ziehen lassen</t>
+          <t>frustriert, enttäuscht, verärgert</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>/tuː stiːp tiː/</t>
+          <t>/ˈfrʌstreɪtɪd/</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Adjektiv</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>To let tea leaves sit in hot water to release flavor and color.</t>
+          <t>Feeling upset or annoyed because of an inability to achieve something.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>You should steep tea for about three to five minutes.</t>
+          <t>I was frustrated that the internet kept cutting out during my presentation.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>She steeped the tea in boiling water before serving it.</t>
-        </is>
-      </c>
-      <c r="I94" t="n">
-        <v>2</v>
+          <t>She felt frustrated when nobody listened to her ideas.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5889,47 +5907,51 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Personally Identifiable Information (PII)</t>
+          <t>relieved</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>personenbezogene Daten</t>
+          <t>erleichtert</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>/ˈpɜːrsənəli aɪˈdentɪfaɪəbl ˌɪnfərˈmeɪʃən/</t>
+          <t>/rɪˈliːvd/</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Adjektiv</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Data that can identify a specific individual, such as name, address, or social security number.</t>
+          <t>Feeling no longer anxious or worried because something difficult has passed.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Companies must protect PII to comply with privacy regulations.</t>
+          <t>He was relieved to hear that his flight was not cancelled.</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Never share your PII with untrusted websites or emails.</t>
-        </is>
-      </c>
-      <c r="I95" t="n">
-        <v>3</v>
+          <t>She felt deeply relieved when she passed the driving test.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5939,17 +5961,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>pointless</t>
+          <t>awkward</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>sinnlos</t>
+          <t>unangenehm, unbeholfen, peinlich</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>/ˈpɔɪntləs/</t>
+          <t>/ˈɔːkwəd/</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5959,27 +5981,31 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Having no purpose, use, or likelihood of success.</t>
+          <t>Causing or feeling social discomfort; difficult to handle or use.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>It's pointless to argue about it now.</t>
+          <t>There was an awkward silence after he made the joke.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>The meeting was completely pointless.</t>
-        </is>
-      </c>
-      <c r="I96" t="n">
-        <v>2</v>
+          <t>She felt awkward being the only person who didn't know anyone at the party.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5989,17 +6015,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>cheerful</t>
+          <t>decent</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>fröhlich</t>
+          <t>anständig, ordentlich, passabel</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>/ˈtʃɪəfəl/</t>
+          <t>/ˈdiːsnt/</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6009,27 +6035,31 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Noticeably happy and optimistic in mood or manner.</t>
+          <t>Of an acceptable standard; morally correct and honest.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>She greeted us with a cheerful smile.</t>
+          <t>The hotel was decent – nothing special, but clean and comfortable.</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>The children were cheerful despite the rain.</t>
-        </is>
-      </c>
-      <c r="I97" t="n">
-        <v>2</v>
+          <t>He is a decent person who always tries to do the right thing.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6039,17 +6069,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>clumsy</t>
+          <t>vivid</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ungeschickt</t>
+          <t>lebhaft, lebendig, intensiv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>/ˈklʌmzi/</t>
+          <t>/ˈvɪvɪd/</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6059,27 +6089,31 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Moving or doing things in an awkward way, often causing accidents or mistakes.</t>
+          <t>Producing powerful feelings or strong, clear images in the mind; bright and strong.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>He is too clumsy to carry those fragile dishes.</t>
+          <t>She had a vivid dream about flying over the mountains.</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>She made a clumsy attempt to catch the ball.</t>
-        </is>
-      </c>
-      <c r="I98" t="n">
-        <v>2</v>
+          <t>The documentary used vivid colours to bring the wildlife to life.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6089,52 +6123,51 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>exploitation</t>
+          <t>compelling</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ausbeutung</t>
+          <t>überzeugend, fesselnd, zwingend</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>/ˌeksplɔɪˈteɪʃən/</t>
+          <t>/kəmˈpelɪŋ/</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Nomen</t>
+          <t>Adjektiv</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>The action of treating someone unfairly to benefit from their work or resources.</t>
+          <t>Evoking interest, attention, or admiration in a powerfully irresistible way.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>The exploitation of workers in factories was common during the industrial revolution.</t>
+          <t>The novel had a compelling storyline that kept me reading all night.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Environmental exploitation leads to the destruction of natural habitats.</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Continental_AG_tire_factory_Mittellandkanal_Stoecken_Hannover_Germany_02.jpg?width=400</t>
-        </is>
-      </c>
-      <c r="I99" t="n">
-        <v>3</v>
+          <t>She made a compelling argument for increasing the budget.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6144,17 +6177,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>invocable</t>
+          <t>grateful</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>aufrufbar</t>
+          <t>dankbar</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>/ɪnˈvoʊkəbl/</t>
+          <t>/ˈɡreɪtfl/</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6164,27 +6197,31 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Capable of being called upon or summoned, especially in programming or legal contexts.</t>
+          <t>Feeling or showing thanks for something received.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>The function is invocable from any part of the code.</t>
+          <t>I am truly grateful for all the help you have given me.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>This right is invocable by any citizen under the law.</t>
-        </is>
-      </c>
-      <c r="I100" t="n">
-        <v>3</v>
+          <t>She was grateful that the rain stopped before the outdoor ceremony.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6194,52 +6231,51 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Pitfall</t>
+          <t>cynical</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Falle, Fallstrick</t>
+          <t>zynisch, misstrauisch</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>/ˈpɪtfɔːl/</t>
+          <t>/ˈsɪnɪkl/</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Nomen</t>
+          <t>Adjektiv</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>A hidden or unexpected danger or difficulty.</t>
+          <t>Believing that people are motivated purely by self-interest; distrustful of human sincerity.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>One pitfall of online shopping is hidden delivery costs.</t>
+          <t>He was cynical about politicians ever keeping their promises.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Avoid the common pitfall of studying only the night before exams.</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Insect_trap_hidden_in_a_tree_trunk_in_Junkerdalsura.jpg?width=400</t>
-        </is>
-      </c>
-      <c r="I101" t="n">
-        <v>2</v>
+          <t>After years in business, she had grown cynical about people's motives.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6249,17 +6285,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>effortless</t>
+          <t>cautious</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>mühelos</t>
+          <t>vorsichtig, behutsam</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>/ˈefətləs/</t>
+          <t>/ˈkɔːʃəs/</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6269,27 +6305,31 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Requiring no physical or mental effort; done with ease.</t>
+          <t>Careful to avoid potential problems or dangers; not taking unnecessary risks.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>She made the difficult task look effortless.</t>
+          <t>She was cautious when crossing the icy road.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>His effortless style impressed everyone at the party.</t>
-        </is>
-      </c>
-      <c r="I102" t="n">
-        <v>2</v>
+          <t>The investors took a cautious approach in the uncertain market.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6299,47 +6339,51 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>to stack</t>
+          <t>mediocre</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>stapeln</t>
+          <t>mittelmäßig, durchschnittlich</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>/stæk/</t>
+          <t>/ˌmiːdiˈoʊkər/</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>Adjektiv</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>To arrange things in a neat pile, one on top of another.</t>
+          <t>Of only moderate quality; not very good; unremarkable.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Please stack the chairs after the meeting.</t>
+          <t>The performance was mediocre – the audience expected much more.</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>She stacked the books on the shelf.</t>
-        </is>
-      </c>
-      <c r="I103" t="n">
-        <v>1</v>
+          <t>He was unhappy with his mediocre exam results.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6349,47 +6393,51 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>to sift</t>
+          <t>bold</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>sieben</t>
+          <t>mutig, gewagt, kühn</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>/sɪft/</t>
+          <t>/boʊld/</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>Adjektiv</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>To pass a substance through a sieve to remove lumps or separate particles.</t>
+          <t>Willing to take risks; showing confidence and courage; not afraid.</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>She sifted the flour before making the cake.</t>
+          <t>It was a bold decision to quit her job and start her own business.</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>They sifted through the evidence to find clues.</t>
-        </is>
-      </c>
-      <c r="I104" t="n">
-        <v>2</v>
+          <t>He wore a bold red jacket that stood out in the crowd.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6399,47 +6447,51 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>to dissolve</t>
+          <t>overwhelming</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>auflösen</t>
+          <t>überwältigend, erdrückend</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>/dɪˈzɒlv/</t>
+          <t>/ˌoʊvərˈwelmɪŋ/</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>Adjektiv</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>To become or cause to become incorporated into a liquid so as to form a solution.</t>
+          <t>Very great in amount or strength; too intense to deal with comfortably.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sugar dissolves quickly in hot water.</t>
+          <t>The response to the charity appeal was overwhelming – thousands donated.</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>The tablet will dissolve in your mouth.</t>
-        </is>
-      </c>
-      <c r="I105" t="n">
-        <v>2</v>
+          <t>She felt an overwhelming sense of relief when the operation was over.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6449,47 +6501,51 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>red tape</t>
+          <t>to achieve</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Bürokratie</t>
+          <t>erreichen, erzielen, schaffen</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>/red teɪp/</t>
+          <t>/tuː əˈtʃiːv/</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Phrase</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Excessive bureaucracy or adherence to rules and formalities, especially in public business.</t>
+          <t>To successfully reach a goal or result through effort or skill.</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>The company struggled with red tape when applying for permits.</t>
+          <t>She worked hard to achieve her dream of becoming a doctor.</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>We need to cut through the red tape to get this approved quickly.</t>
-        </is>
-      </c>
-      <c r="I106" t="n">
-        <v>2</v>
+          <t>The team achieved great results despite limited resources.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6499,47 +6555,51 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>distorted</t>
+          <t>to adapt</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>verzerrt</t>
+          <t>sich anpassen, adaptieren</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>/dɪˈstɔːtɪd/</t>
+          <t>/tuː əˈdæpt/</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Adjektiv</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Changed from the original shape, sound, or meaning in an unusual way.</t>
+          <t>To change or adjust to suit new conditions or requirements.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>The mirror showed a distorted reflection of my face.</t>
+          <t>It took him a while to adapt to the new working environment.</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>The audio was distorted and hard to understand.</t>
-        </is>
-      </c>
-      <c r="I107" t="n">
-        <v>2</v>
+          <t>Animals adapt to their surroundings over thousands of years.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6549,52 +6609,51 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>to appreciate</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Beibehaltung</t>
+          <t>schätzen, würdigen, zu schätzen wissen</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>/rɪˈtenʃən/</t>
+          <t>/tuː əˈpriːʃieɪt/</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Nomen</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>The continued possession, use, or control of something.</t>
+          <t>To recognise and value the good qualities of something or someone.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Customer retention is crucial for business success.</t>
+          <t>I really appreciate everything you have done to help me.</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>The company improved employee retention through better benefits.</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Mercy_Health_Partners_of_Southwest_Ohio_senior_health_and_housing_services_recruitment_and_retention_(R_&amp;_R)_initiative_-_DPLA_-_b80e071d7a1f9ae003c0c81c7ceacd77.jpg?width=400</t>
-        </is>
-      </c>
-      <c r="I108" t="n">
-        <v>2</v>
+          <t>He didn't appreciate how hard she worked until she left.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6604,47 +6663,51 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>pensive</t>
+          <t>to assume</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nachdenklich</t>
+          <t>annehmen, vermuten, voraussetzen</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>/ˈpensɪv/</t>
+          <t>/tuː əˈsjuːm/</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Adjektiv</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Engaged in deep or serious thought, often with a hint of sadness.</t>
+          <t>To accept something as true without proof; to take for granted.</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>She had a pensive look on her face.</t>
+          <t>Don't assume everyone shares your opinion – ask first.</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>He sat pensive by the window, thinking about his future.</t>
-        </is>
-      </c>
-      <c r="I109" t="n">
-        <v>2</v>
+          <t>I assumed he would be late, but he actually arrived early.</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6654,48 +6717,4102 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>blunt</t>
+          <t>to avoid</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>stumpf, direkt</t>
+          <t>vermeiden, meiden, ausweichen</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>/blʌnt/</t>
+          <t>/tuː əˈvɔɪd/</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Adjektiv</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Not sharp or pointed; saying what you think without trying to be polite.</t>
+          <t>To keep away from or stop oneself from doing something.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>The knife was too blunt to cut the bread.</t>
+          <t>Try to avoid eating too much sugar if you want to stay healthy.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>She was very blunt and told him the truth.</t>
-        </is>
-      </c>
-      <c r="I110" t="n">
-        <v>2</v>
+          <t>She avoided making eye contact during the difficult conversation.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>to challenge</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>herausfordern, infrage stellen</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>/tuː ˈtʃælɪndʒ/</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>To question or dispute something; to test someone's abilities.</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>The new CEO challenged the way the company had always done things.</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>This role will challenge you in ways you have never experienced before.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>to convince</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>überzeugen, überreden</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>/tuː kənˈvɪns/</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>To persuade someone to believe something or to do something.</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>He convinced his boss to give the team an extra day off.</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>I couldn't convince her that the film was worth watching.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>to demand</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>fordern, verlangen, beanspruchen</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>/tuː dɪˈmɑːnd/</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>To ask for something forcefully and insistently; to require.</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>The workers demanded better pay and working conditions.</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Teaching demands a great deal of patience and dedication.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>to emphasize</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>betonen, hervorheben, unterstreichen</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>/tuː ˈemfəsaɪz/</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>To give special importance or prominence to something.</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>The teacher emphasized the importance of reading every day.</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>She emphasized that the deadline was non-negotiable.</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>to encourage</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ermutigen, fördern, bestärken</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>/tuː ɪnˈkʌrɪdʒ/</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>To give support, confidence, or hope to someone; to motivate.</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>His parents always encouraged him to pursue his passion for music.</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>The coach encouraged the team after a difficult first half.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>to hesitate</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>zögern, zaudern, innehalten</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>/tuː ˈhezɪteɪt/</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>To pause before doing or saying something, often due to uncertainty.</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>She hesitated before answering the difficult question.</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Don't hesitate to call me if you need any help.</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>to influence</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>beeinflussen, prägen</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>/tuː ˈɪnfluəns/</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>To have an effect on the character, development, or behaviour of someone or something.</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>His teacher influenced him to study architecture.</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Social media can heavily influence the way young people see themselves.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>to negotiate</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>verhandeln, aushandeln</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>/tuː nɪˈɡoʊʃieɪt/</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>To discuss something in order to reach an agreement.</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>They negotiated a better deal by staying calm and prepared.</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>The union negotiated improved holiday allowances for all staff.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>to overcome</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>überwinden, bewältigen, besiegen</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>/tuː ˌoʊvərˈkʌm/</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>To succeed in dealing with or gaining control over something difficult.</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>She overcame her fear of public speaking after joining a drama group.</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>He worked hard to overcome the obstacles in his path.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>to pursue</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>verfolgen, anstreben, nachgehen</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>/tuː pərˈsjuː/</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>To follow or chase something; to continue to work towards a goal.</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>She decided to pursue a career in journalism.</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>The police pursued the suspect through the city streets.</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>to recognize</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>erkennen, anerkennen, identifizieren</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>/tuː ˈrekəɡnaɪz/</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>To identify someone or something from previous experience; to acknowledge officially.</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>I recognized her immediately even though I hadn't seen her in ten years.</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>The company was recognized for its outstanding customer service.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>to rely on</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>sich verlassen auf, abhängen von</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>/tuː rɪˈlaɪ ɒn/</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>To trust or depend on someone or something.</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>You can always rely on her to get the job done on time.</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>He relied on public transport to get to work every day.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>to reveal</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>enthüllen, offenbaren, bekannt geben</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>/tuː rɪˈviːl/</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>To make something unknown or hidden known to others.</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>The documentary revealed shocking facts about the food industry.</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>She finally revealed the secret she had been keeping for years.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>to suspect</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>vermuten, verdächtigen, ahnen</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>/tuː səˈspekt/</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>To believe something is likely or possible; to think someone may be guilty.</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>I suspect he didn't finish the report on time.</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>The police suspected the neighbour from the very beginning.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>to witness</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>bezeugen, miterleben, Zeuge sein von</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>/tuː ˈwɪtnɪs/</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>To see an event happen, especially an important or significant one.</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>She witnessed the accident from her kitchen window.</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>We are witnessing a major shift in the way people communicate.</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Achievement</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>die Leistung, der Erfolg, die Errungenschaft</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>/əˈtʃiːvmənt/</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>A thing done successfully, typically by effort, courage, or skill.</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Winning the championship was the greatest achievement of his career.</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Learning a new language is a remarkable achievement at any age.</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Approach</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>der Ansatz, die Herangehensweise, der Zugang</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>/əˈproʊtʃ/</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>A way of dealing with a situation or problem; a method or strategy.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>We need a fresh approach to solve this long-standing problem.</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Her calm approach to conflict made her an effective manager.</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>das Argument, der Streit, die Auseinandersetzung</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>/ˈɑːɡjumənt/</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>A reason given to support or oppose an idea; also a heated disagreement.</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>He made a convincing argument for changing the company policy.</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>They had a serious argument about money and didn't speak for a week.</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Attitude</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>die Einstellung, die Haltung, die Mentalität</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>/ˈætɪtjuːd/</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>A settled way of thinking or feeling about something; one's outlook or stance.</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Her positive attitude helped the team stay motivated during tough times.</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>You need to change your attitude if you want to succeed.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Challenge</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>die Herausforderung, die Aufgabe</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>/ˈtʃælɪndʒ/</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>A difficult task or situation that tests someone's abilities.</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Moving abroad was the biggest challenge she had ever faced.</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>The main challenge is keeping costs low while improving quality.</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Circumstance</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>der Umstand, die Situation, die Lage</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>/ˈsɜːkəmstæns/</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>A fact or condition connected with or relevant to an event or action.</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Given the circumstances, she handled the crisis extremely well.</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Under no circumstance should you share your password with anyone.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Commitment</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>das Engagement, die Verpflichtung, die Hingabe</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>/kəˈmɪtmənt/</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>The state of being dedicated to a cause, activity, or relationship.</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>His commitment to the project was evident from day one.</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Marriage is a serious commitment that requires work from both partners.</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Concern</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>die Sorge, das Anliegen, das Bedenken</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>/kənˈsɜːn/</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>A matter of interest or importance; a feeling of worry.</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Safety is our main concern on every construction site.</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>She expressed concern about the rising cost of living.</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Conflict</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>der Konflikt, der Streit, der Widerspruch</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>/ˈkɒnflɪkt/</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>A serious disagreement or argument; a prolonged armed struggle.</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>The conflict between the two departments was slowing everything down.</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>The UN is working to resolve the conflict peacefully.</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Consequence</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>die Konsequenz, die Folge, das Ergebnis</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>/ˈkɒnsɪkwəns/</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>A result or effect of an action or condition.</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>He didn't study and, as a consequence, he failed the exam.</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>We must consider the consequences of our decisions carefully.</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>der Kontext, der Zusammenhang, die Umgebung</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>/ˈkɒntekst/</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>The circumstances surrounding an event or statement that help explain its meaning.</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>You need to read the full article to understand the context of the quote.</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>This word has a different meaning depending on the context.</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Dilemma</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>das Dilemma, die Zwickmühle</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>/dɪˈlemə/</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>A situation where a difficult choice has to be made between two equally undesirable alternatives.</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>She faced a dilemma: take the higher-paying job or stay closer to family.</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>The ethical dilemma had no easy answer.</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>der Beweis, die Belege, das Beweismaterial</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>/ˈevɪdəns/</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Facts or information indicating whether a belief or proposition is true.</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>The police found no evidence linking him to the crime.</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>There is growing evidence that exercise improves mental health.</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Failure</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>das Scheitern, der Misserfolg, der Ausfall</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>/ˈfeɪljər/</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Lack of success; the omission of expected or required action.</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>He saw every failure as a learning opportunity, not a setback.</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>The power failure left half the city without electricity.</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Habit</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>die Gewohnheit, die Angewohnheit</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>/ˈhæbɪt/</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>A settled or regular tendency or practice, especially one that is hard to give up.</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>She developed the habit of reading before bed to unwind.</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Smoking is a habit that is very difficult to break.</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>die Auswirkung, der Einfluss, der Aufprall</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>/ˈɪmpækt/</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>A marked effect or influence on something or someone.</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>The new law had a major impact on small businesses.</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Climate change is having a devastating impact on coral reefs.</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Intention</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>die Absicht, das Vorhaben, die Intention</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>/ɪnˈtenʃn/</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>A thing intended; an aim or plan.</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>His intention was to apologise, but he never found the right moment.</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>I have every intention of finishing this project on time.</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>die Gelegenheit, die Chance, die Möglichkeit</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>/ˌɒpəˈtjuːnɪti/</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>A set of circumstances that makes it possible to do something desirable.</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>This job offer is a fantastic opportunity that she shouldn't miss.</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>He seized every opportunity to practise his English.</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Perspective</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>die Perspektive, die Sichtweise, der Blickwinkel</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>/pəˈspektɪv/</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>A particular attitude towards or way of regarding something; a point of view.</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Travelling abroad gave her a completely new perspective on life.</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>It is important to consider the situation from different perspectives.</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>die Priorität, der Vorrang</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>/praɪˈɒrɪti/</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>A thing regarded as more important than others; the fact of being treated first.</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Health should always be your number one priority.</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>The government set education as its top priority for the coming year.</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Responsibility</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>die Verantwortung, die Pflicht, die Zuständigkeit</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>/rɪˌspɒnsɪˈbɪlɪti/</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>The state or fact of having a duty to deal with something; being accountable.</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>As a parent, you have a responsibility to keep your children safe.</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>She took full responsibility for the mistake and apologised publicly.</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>die Belohnung, die Anerkennung, der Lohn</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>/rɪˈwɔːd/</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>A thing given in recognition of service, effort, or achievement.</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Hard work should be met with fair reward.</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>They offered a reward for anyone who could find the lost dog.</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>das Risiko, die Gefahr, das Wagnis</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>/rɪsk/</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>A situation involving exposure to danger or the chance of something going wrong.</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Starting a business always involves a certain amount of risk.</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>There is a risk of flooding in low-lying areas after heavy rain.</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>die Lösung, die Auflösung</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>/səˈluːʃn/</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>A means of solving a problem or dealing with a difficult situation.</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>We need to find a long-term solution to the traffic problem.</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Talking it through calmly is often the best solution to an argument.</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>die Strategie, der Plan, das Konzept</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>/ˈstrætɪdʒi/</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>A plan of action designed to achieve a long-term or overall goal.</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>The company needs a clear strategy to compete in the global market.</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Playing chess requires careful strategy and forward thinking.</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Struggle</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>der Kampf, die Mühe, das Ringen</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>/ˈstrʌɡl/</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>A very difficult task or situation; a determined effort under difficulties.</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>The struggle to balance work and family life is something many people share.</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>The documentary showed the daily struggle of people living in poverty.</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Trust</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>das Vertrauen, das Zutrauen</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>/trʌst/</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Firm belief in the reliability, truth, or ability of someone or something.</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Trust is the foundation of every healthy relationship.</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>It took years to rebuild the trust after he had lied.</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Uncertainty</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>die Unsicherheit, die Ungewissheit, der Zweifel</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>/ʌnˈsɜːtnti/</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>The state of being uncertain or not sure about something; unpredictability.</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>The economic uncertainty made investors hesitant to commit large sums.</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Living with uncertainty is a skill that requires practise and resilience.</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>das Bewusstsein, die Aufmerksamkeit, das Wissen</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>/əˈweənɪs/</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Knowledge or perception of a situation or fact; being conscious of something.</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>The campaign aims to raise awareness about mental health issues.</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Her awareness of other people's feelings made her an excellent therapist.</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Tension</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>die Spannung, die Anspannung, die Reibung</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>/ˈtenʃn/</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Mental or emotional strain; a strained relationship between people or groups.</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>There was visible tension between the two colleagues after the argument.</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>The film builds tension slowly before the shocking final scene.</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>to figure out</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>herausfinden, verstehen, lösen</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>/tuː ˈfɪɡər aʊt/</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>To understand or discover something; to find the answer to a problem.</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>I couldn't figure out how to use the new software at first.</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>She finally figured out why the machine kept stopping.</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>to give up</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>aufgeben, kapitulieren</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>/tuː ɡɪv ʌp/</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>To stop trying to do something; to admit defeat or surrender.</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Don't give up – you are almost there!</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>He gave up smoking after twenty years.</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>to look forward to</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>sich freuen auf (etwas)</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>/tuː lʊk ˈfɔːwəd tuː/</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>To feel excited or pleased about something that is going to happen.</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>I am really looking forward to our holiday next week.</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>She looks forward to her morning coffee every single day.</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>to stand out</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>herausstechen, auffallen, sich abheben</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>/tuː stænd aʊt/</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>To be clearly better or more noticeable than others; to be conspicuous.</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Her bright yellow coat made her stand out in the crowd.</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>His creative approach made his application stand out from all the others.</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>to catch up</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>aufholen, nachholen, auf den neuesten Stand kommen</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>/tuː kætʃ ʌp/</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>To reach the same level or standard as others; to exchange news with someone.</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>He missed three weeks of school and needed time to catch up.</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Let's have coffee soon – I'd love to catch up with you.</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>to put off</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>aufschieben, verschieben, vertagen</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>/tuː pʊt ɒf/</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>To postpone or delay doing something; also to cause someone to lose interest.</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Stop putting off the dentist appointment – just book it!</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>The constant noise was putting her off her work.</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>to come across</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>stoßen auf, wirken, einen Eindruck machen</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>/tuː kʌm əˈkrɒs/</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>To meet or find something by chance; to give a particular impression to others.</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>I came across an old photo album while tidying the attic.</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>He came across as very confident during the interview.</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>to make up your mind</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>sich entscheiden, einen Entschluss fassen</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>/tuː meɪk ʌp jɔː maɪnd/</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>To decide between two or more options after thinking carefully.</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Have you made up your mind about which university to apply to?</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>I can't make up my mind – both options have their advantages.</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>to keep in mind</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>im Hinterkopf behalten, berücksichtigen</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>/tuː kiːp ɪn maɪnd/</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>To remember or consider something as important when thinking or deciding.</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Keep in mind that the deadline is Friday, not Monday.</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Please keep in mind that we have a limited budget for this project.</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>to take for granted</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>als selbstverständlich ansehen, nicht schätzen</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>/tuː teɪk fər ˈɡrɑːntɪd/</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>To fail to appreciate the value of something because you are so used to it.</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Don't take your health for granted – look after yourself.</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>He took his friends for granted until they were no longer around.</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>to run out of</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ausgehen, aufbrauchen, keinen ... mehr haben</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>/tuː rʌn aʊt ɒv/</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>To use up the entire supply of something; to have none left.</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>We ran out of milk, so I need to go to the shop.</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>The car ran out of petrol on the motorway.</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>to get along with</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>gut auskommen mit, sich gut verstehen mit</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>/tuː ɡet əˈlɒŋ wɪð/</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>To have a friendly relationship with someone; to be on good terms.</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>She gets along with all of her colleagues really well.</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Do you think the new flatmates will get along with each other?</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>to point out</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>hinweisen auf, aufzeigen, darauf aufmerksam machen</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>/tuː pɔɪnt aʊt/</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>To direct attention to something; to mention something that might be overlooked.</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>She pointed out several errors in the report before it was submitted.</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Can you point out the house on the map?</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>to bring up</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>ansprechen, erwähnen, aufbringen (Thema)</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>/tuː brɪŋ ʌp/</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>To mention a topic in conversation; also to raise a child.</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>He brought up the issue of overtime pay at the team meeting.</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>She was brought up by her grandparents in a small village.</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>to carry on</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>weitermachen, fortfahren, nicht aufhören</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>/tuː ˈkæri ɒn/</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>To continue doing something; to proceed despite difficulties.</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Carry on – you are doing a great job!</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>They carried on working even when the power went out.</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Suspense</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>die Spannung, die Ungewissheit (Thriller)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>/səˈspens/</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>A feeling of excited or anxious uncertainty about what may happen.</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>The director builds suspense slowly throughout the entire first act.</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>The book kept me in suspense right until the final page.</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Plot twist</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>die Wendung in der Geschichte, der überraschende Handlungsverlauf</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>/plɒt twɪst/</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>An unexpected development in a story that changes the direction of the narrative.</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Nobody saw the plot twist coming – it completely changed the story.</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>The best plot twists make you want to rewatch the whole film.</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Cliffhanger</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>der Cliffhanger, das spannende offene Ende</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>/ˈklɪfhæŋər/</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>An ending to a story or episode that leaves the audience in suspense.</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>The season ended on a cliffhanger – we have no idea if she survived.</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Soap operas are famous for their dramatic cliffhangers.</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Protagonist</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>der Protagonist, die Hauptfigur</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>/proʊˈtæɡənɪst/</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>The main character in a story, film, or play; the hero or central figure.</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>The protagonist of the series is a detective with a troubled past.</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>We follow the protagonist on her journey from poverty to success.</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Antagonist</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>der Antagonist, der Bösewicht, der Gegenspieler</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>/ænˈtæɡənɪst/</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>A person who actively opposes the protagonist; the villain of a story.</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>The antagonist was so well written that audiences almost sympathised with him.</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>A great story needs a compelling antagonist, not just a great hero.</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Flashback</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>der Rückblick, die Rückblende</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>/ˈflæʃbæk/</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>A scene in a film or story set in a time earlier than the main action.</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>The episode uses a flashback to explain the character's troubled childhood.</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>The film cuts to a flashback every time she hears that song.</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Foreshadowing</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>die Vorausdeutung, die Andeutung</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>/fɔːˈʃædoʊɪŋ/</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>A hint or warning of a future event in a story or film.</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>The ominous music in the opening scene was clear foreshadowing.</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Looking back, the foreshadowing was obvious – we just didn't notice it at first.</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Spoiler</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>der Spoiler, die unerwünschte Enthüllung</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>/ˈspɔɪlər/</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>A piece of information that reveals important plot details before someone has seen a film or read a book.</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Warning: the next paragraph contains spoilers for the latest episode.</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>He accidentally gave away a major spoiler and everyone was furious.</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Binge-watch</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Serien am Stück schauen, Serienmarathon machen</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>/ˈbɪndʒ wɒtʃ/</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>To watch multiple episodes of a TV show in rapid succession.</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>We binge-watched the entire series over the long weekend.</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>She binge-watched three seasons of the show without leaving the sofa.</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Season finale</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>das Staffelfinale, der letzte Teil einer Staffel</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>/ˈsiːzn fɪˈnɑːli/</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>The last episode of a television season, often with a dramatic conclusion.</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>The season finale left millions of fans desperate for the next series.</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>She stayed up until 2 a.m. to watch the season finale live.</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Subplot</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>die Nebenhandlung, der Nebenstrang</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>/ˈsʌbplɒt/</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>A secondary plot that runs alongside the main storyline in a film or book.</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>The romantic subplot added depth and warmth to the action film.</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>A well-crafted subplot can be just as engaging as the main story.</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Character development</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>die Charakterentwicklung</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>/ˈkærɪktər dɪˈveləpmənt/</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>The process by which a character in a story changes and grows over time.</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>The show's character development is what keeps viewers coming back for more.</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Critics praised the film for its exceptional character development.</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>die Erzählung, das Narrativ, die Geschichte</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>/ˈnærətɪv/</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>A spoken or written account of connected events; the art or process of storytelling.</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>The film's narrative jumps between three different timelines.</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>She used personal narrative to make her speech more engaging.</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Genre</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>das Genre, die Gattung, die Stilrichtung</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>/ˈʒɒnrə/</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>A category of artistic composition, characterised by a particular style or form.</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Crime drama is her favourite genre – she never gets tired of it.</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>The film blends the sci-fi and horror genres in a unique way.</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Screenplay</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>das Drehbuch</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>/ˈskriːnpleɪ/</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>The script of a film, including dialogue and directions.</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>She spent three years writing the screenplay for her debut film.</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>The screenplay won an Oscar before the film was even shot.</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr">
         <is>
           <t>TV</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vokabeln" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fortschritt" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Vokabeln" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fortschritt" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L185"/>
+  <dimension ref="A1:L186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5454,7 +5454,6 @@
           <t>There is a significant difference between the two proposals.</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>B1</t>
@@ -5465,7 +5464,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5508,7 +5506,6 @@
           <t>He made a subtle hint that he wanted to leave early.</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>B2</t>
@@ -5519,7 +5516,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5562,7 +5558,6 @@
           <t>He showed a genuine interest in learning the language.</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>B1</t>
@@ -5573,7 +5568,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5616,7 +5610,6 @@
           <t>The film's special effects were absolutely remarkable.</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>B1</t>
@@ -5627,7 +5620,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5670,7 +5662,6 @@
           <t>It was considerate of her to send a thank-you note.</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>B2</t>
@@ -5681,7 +5672,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5724,7 +5714,6 @@
           <t>The persistent rain ruined our picnic plans.</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>B2</t>
@@ -5735,7 +5724,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5778,7 +5766,6 @@
           <t>She felt anxious waiting for the doctor's call.</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>B1</t>
@@ -5789,7 +5776,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5832,7 +5818,6 @@
           <t>He looked exhausted after working three back-to-back night shifts.</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>A2</t>
@@ -5843,7 +5828,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5886,7 +5870,6 @@
           <t>She felt frustrated when nobody listened to her ideas.</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>A2</t>
@@ -5897,7 +5880,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5940,7 +5922,6 @@
           <t>She felt deeply relieved when she passed the driving test.</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>B1</t>
@@ -5951,7 +5932,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -5994,7 +5974,6 @@
           <t>She felt awkward being the only person who didn't know anyone at the party.</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>B1</t>
@@ -6005,7 +5984,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6048,7 +6026,6 @@
           <t>He is a decent person who always tries to do the right thing.</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>B1</t>
@@ -6059,7 +6036,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6102,7 +6078,6 @@
           <t>The documentary used vivid colours to bring the wildlife to life.</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>B2</t>
@@ -6113,7 +6088,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6156,7 +6130,6 @@
           <t>She made a compelling argument for increasing the budget.</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>C1</t>
@@ -6167,7 +6140,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6210,7 +6182,6 @@
           <t>She was grateful that the rain stopped before the outdoor ceremony.</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>A2</t>
@@ -6221,7 +6192,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6264,7 +6234,6 @@
           <t>After years in business, she had grown cynical about people's motives.</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>C1</t>
@@ -6275,7 +6244,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6318,7 +6286,6 @@
           <t>The investors took a cautious approach in the uncertain market.</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>B1</t>
@@ -6329,7 +6296,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6372,7 +6338,6 @@
           <t>He was unhappy with his mediocre exam results.</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>B2</t>
@@ -6383,7 +6348,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6426,7 +6390,6 @@
           <t>He wore a bold red jacket that stood out in the crowd.</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>B1</t>
@@ -6437,7 +6400,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6480,7 +6442,6 @@
           <t>She felt an overwhelming sense of relief when the operation was over.</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>B2</t>
@@ -6491,7 +6452,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6534,7 +6494,6 @@
           <t>The team achieved great results despite limited resources.</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>A2</t>
@@ -6545,7 +6504,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6588,7 +6546,6 @@
           <t>Animals adapt to their surroundings over thousands of years.</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>B1</t>
@@ -6599,7 +6556,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6642,7 +6598,6 @@
           <t>He didn't appreciate how hard she worked until she left.</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>B1</t>
@@ -6653,7 +6608,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6696,7 +6650,6 @@
           <t>I assumed he would be late, but he actually arrived early.</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>B1</t>
@@ -6707,7 +6660,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6750,7 +6702,6 @@
           <t>She avoided making eye contact during the difficult conversation.</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>A2</t>
@@ -6761,7 +6712,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6804,7 +6754,6 @@
           <t>This role will challenge you in ways you have never experienced before.</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>B1</t>
@@ -6815,7 +6764,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6858,7 +6806,6 @@
           <t>I couldn't convince her that the film was worth watching.</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>B1</t>
@@ -6869,7 +6816,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6912,7 +6858,6 @@
           <t>Teaching demands a great deal of patience and dedication.</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>B1</t>
@@ -6923,7 +6868,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -6966,7 +6910,6 @@
           <t>She emphasized that the deadline was non-negotiable.</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>B2</t>
@@ -6977,7 +6920,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7020,7 +6962,6 @@
           <t>The coach encouraged the team after a difficult first half.</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>B1</t>
@@ -7031,7 +6972,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7074,7 +7014,6 @@
           <t>Don't hesitate to call me if you need any help.</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>B1</t>
@@ -7085,7 +7024,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7128,7 +7066,6 @@
           <t>Social media can heavily influence the way young people see themselves.</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>B1</t>
@@ -7139,7 +7076,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7182,7 +7118,6 @@
           <t>The union negotiated improved holiday allowances for all staff.</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>B2</t>
@@ -7193,7 +7128,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7236,7 +7170,6 @@
           <t>He worked hard to overcome the obstacles in his path.</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>B1</t>
@@ -7247,7 +7180,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7290,7 +7222,6 @@
           <t>The police pursued the suspect through the city streets.</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>B2</t>
@@ -7301,7 +7232,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7344,7 +7274,6 @@
           <t>The company was recognized for its outstanding customer service.</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>A2</t>
@@ -7355,7 +7284,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7398,7 +7326,6 @@
           <t>He relied on public transport to get to work every day.</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>B1</t>
@@ -7409,7 +7336,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7452,7 +7378,6 @@
           <t>She finally revealed the secret she had been keeping for years.</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>B1</t>
@@ -7463,7 +7388,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7506,7 +7430,6 @@
           <t>The police suspected the neighbour from the very beginning.</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>B1</t>
@@ -7517,7 +7440,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7560,7 +7482,6 @@
           <t>We are witnessing a major shift in the way people communicate.</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>B2</t>
@@ -7571,7 +7492,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7614,7 +7534,6 @@
           <t>Learning a new language is a remarkable achievement at any age.</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>B1</t>
@@ -7625,7 +7544,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7668,7 +7586,6 @@
           <t>Her calm approach to conflict made her an effective manager.</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>B1</t>
@@ -7679,7 +7596,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7722,7 +7638,6 @@
           <t>They had a serious argument about money and didn't speak for a week.</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>A2</t>
@@ -7733,7 +7648,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7776,7 +7690,6 @@
           <t>You need to change your attitude if you want to succeed.</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>B1</t>
@@ -7787,7 +7700,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7830,7 +7742,6 @@
           <t>The main challenge is keeping costs low while improving quality.</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>B1</t>
@@ -7841,7 +7752,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7884,7 +7794,6 @@
           <t>Under no circumstance should you share your password with anyone.</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>B2</t>
@@ -7895,7 +7804,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7938,7 +7846,6 @@
           <t>Marriage is a serious commitment that requires work from both partners.</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>B2</t>
@@ -7949,7 +7856,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -7992,7 +7898,6 @@
           <t>She expressed concern about the rising cost of living.</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>B1</t>
@@ -8003,7 +7908,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -8046,7 +7950,6 @@
           <t>The UN is working to resolve the conflict peacefully.</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>B1</t>
@@ -8057,7 +7960,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -8100,7 +8002,6 @@
           <t>We must consider the consequences of our decisions carefully.</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>B2</t>
@@ -8111,7 +8012,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -8154,7 +8054,6 @@
           <t>This word has a different meaning depending on the context.</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>B2</t>
@@ -8165,7 +8064,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -8208,7 +8106,6 @@
           <t>The ethical dilemma had no easy answer.</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>B2</t>
@@ -8219,7 +8116,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -8262,7 +8158,6 @@
           <t>There is growing evidence that exercise improves mental health.</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>B1</t>
@@ -8273,7 +8168,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -8316,7 +8210,6 @@
           <t>The power failure left half the city without electricity.</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>B1</t>
@@ -8327,7 +8220,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -8370,7 +8262,6 @@
           <t>Smoking is a habit that is very difficult to break.</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>A2</t>
@@ -8381,7 +8272,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -8424,7 +8314,6 @@
           <t>Climate change is having a devastating impact on coral reefs.</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>B1</t>
@@ -8435,7 +8324,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -8478,7 +8366,6 @@
           <t>I have every intention of finishing this project on time.</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>B2</t>
@@ -8489,7 +8376,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -8532,7 +8418,6 @@
           <t>He seized every opportunity to practise his English.</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>B1</t>
@@ -8543,7 +8428,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -8586,7 +8470,6 @@
           <t>It is important to consider the situation from different perspectives.</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
           <t>B2</t>
@@ -8597,7 +8480,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -8640,7 +8522,6 @@
           <t>The government set education as its top priority for the coming year.</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>B2</t>
@@ -8651,7 +8532,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -8694,7 +8574,6 @@
           <t>She took full responsibility for the mistake and apologised publicly.</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>B1</t>
@@ -8705,7 +8584,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -8748,7 +8626,6 @@
           <t>They offered a reward for anyone who could find the lost dog.</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>B1</t>
@@ -8759,7 +8636,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -8802,7 +8678,6 @@
           <t>There is a risk of flooding in low-lying areas after heavy rain.</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>A2</t>
@@ -8813,7 +8688,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -8856,7 +8730,6 @@
           <t>Talking it through calmly is often the best solution to an argument.</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>A2</t>
@@ -8867,7 +8740,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -8910,7 +8782,6 @@
           <t>Playing chess requires careful strategy and forward thinking.</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>B2</t>
@@ -8921,7 +8792,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -8964,7 +8834,6 @@
           <t>The documentary showed the daily struggle of people living in poverty.</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>B1</t>
@@ -8975,7 +8844,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9018,7 +8886,6 @@
           <t>It took years to rebuild the trust after he had lied.</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>A2</t>
@@ -9029,7 +8896,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9072,7 +8938,6 @@
           <t>Living with uncertainty is a skill that requires practise and resilience.</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9083,7 +8948,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9126,7 +8990,6 @@
           <t>Her awareness of other people's feelings made her an excellent therapist.</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9137,7 +9000,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9180,7 +9042,6 @@
           <t>The film builds tension slowly before the shocking final scene.</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>B1</t>
@@ -9191,7 +9052,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9234,7 +9094,6 @@
           <t>She finally figured out why the machine kept stopping.</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>B1</t>
@@ -9245,7 +9104,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9288,7 +9146,6 @@
           <t>He gave up smoking after twenty years.</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
           <t>A2</t>
@@ -9299,7 +9156,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9342,7 +9198,6 @@
           <t>She looks forward to her morning coffee every single day.</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
           <t>A2</t>
@@ -9353,7 +9208,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9396,7 +9250,6 @@
           <t>His creative approach made his application stand out from all the others.</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
           <t>B1</t>
@@ -9407,7 +9260,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9450,7 +9302,6 @@
           <t>Let's have coffee soon – I'd love to catch up with you.</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>B1</t>
@@ -9461,7 +9312,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9504,7 +9354,6 @@
           <t>The constant noise was putting her off her work.</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>B1</t>
@@ -9515,7 +9364,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9558,7 +9406,6 @@
           <t>He came across as very confident during the interview.</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9569,7 +9416,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9612,7 +9458,6 @@
           <t>I can't make up my mind – both options have their advantages.</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>B1</t>
@@ -9623,7 +9468,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9666,7 +9510,6 @@
           <t>Please keep in mind that we have a limited budget for this project.</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
           <t>B1</t>
@@ -9677,7 +9520,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9720,7 +9562,6 @@
           <t>He took his friends for granted until they were no longer around.</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9731,7 +9572,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9774,7 +9614,6 @@
           <t>The car ran out of petrol on the motorway.</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>B1</t>
@@ -9785,7 +9624,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9828,7 +9666,6 @@
           <t>Do you think the new flatmates will get along with each other?</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>B1</t>
@@ -9839,7 +9676,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9882,7 +9718,6 @@
           <t>Can you point out the house on the map?</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
           <t>B1</t>
@@ -9893,7 +9728,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9936,7 +9770,6 @@
           <t>She was brought up by her grandparents in a small village.</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9947,7 +9780,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -9990,7 +9822,6 @@
           <t>They carried on working even when the power went out.</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>A2</t>
@@ -10001,7 +9832,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -10044,7 +9874,6 @@
           <t>The book kept me in suspense right until the final page.</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
           <t>B1</t>
@@ -10055,7 +9884,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
           <t>TV</t>
@@ -10098,7 +9926,6 @@
           <t>The best plot twists make you want to rewatch the whole film.</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>B1</t>
@@ -10109,7 +9936,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
           <t>TV</t>
@@ -10152,7 +9978,6 @@
           <t>Soap operas are famous for their dramatic cliffhangers.</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>B2</t>
@@ -10163,7 +9988,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
           <t>TV</t>
@@ -10206,7 +10030,6 @@
           <t>We follow the protagonist on her journey from poverty to success.</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>B2</t>
@@ -10217,7 +10040,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
           <t>TV</t>
@@ -10260,7 +10082,6 @@
           <t>A great story needs a compelling antagonist, not just a great hero.</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
           <t>C1</t>
@@ -10271,7 +10092,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
           <t>TV</t>
@@ -10314,7 +10134,6 @@
           <t>The film cuts to a flashback every time she hears that song.</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>B1</t>
@@ -10325,7 +10144,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
           <t>TV</t>
@@ -10368,7 +10186,6 @@
           <t>Looking back, the foreshadowing was obvious – we just didn't notice it at first.</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
           <t>C1</t>
@@ -10379,7 +10196,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
           <t>TV</t>
@@ -10422,7 +10238,6 @@
           <t>He accidentally gave away a major spoiler and everyone was furious.</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>A2</t>
@@ -10433,7 +10248,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
           <t>TV</t>
@@ -10476,7 +10290,6 @@
           <t>She binge-watched three seasons of the show without leaving the sofa.</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
           <t>A2</t>
@@ -10487,7 +10300,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
           <t>TV</t>
@@ -10530,7 +10342,6 @@
           <t>She stayed up until 2 a.m. to watch the season finale live.</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>A2</t>
@@ -10541,7 +10352,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
           <t>TV</t>
@@ -10584,7 +10394,6 @@
           <t>A well-crafted subplot can be just as engaging as the main story.</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
           <t>C1</t>
@@ -10595,7 +10404,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
           <t>TV</t>
@@ -10638,7 +10446,6 @@
           <t>Critics praised the film for its exceptional character development.</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>B2</t>
@@ -10649,7 +10456,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
           <t>TV</t>
@@ -10692,7 +10498,6 @@
           <t>She used personal narrative to make her speech more engaging.</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
           <t>C1</t>
@@ -10703,7 +10508,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
           <t>TV</t>
@@ -10746,7 +10550,6 @@
           <t>The film blends the sci-fi and horror genres in a unique way.</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
           <t>B1</t>
@@ -10757,7 +10560,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
           <t>TV</t>
@@ -10800,7 +10602,6 @@
           <t>The screenplay won an Oscar before the film was even shot.</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>B2</t>
@@ -10811,10 +10612,61 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
           <t>TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>meanest</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>gemeinste, niederträchtigste</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>/ˈmiːnɪst/</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Superlative form of mean; most unkind or cruel</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>That was the meanest thing anyone has ever said to me.</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>He is the meanest person I have ever met.</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="n">
+        <v>2</v>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
         </is>
       </c>
     </row>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L186"/>
+  <dimension ref="A1:L187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10654,7 +10654,6 @@
           <t>He is the meanest person I have ever met.</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="n">
         <v>2</v>
       </c>
@@ -10663,8 +10662,63 @@
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Lunatic</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Verrückter</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>/ˈluː.nə.tɪk/</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>A person who behaves in a foolish or crazy way.</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>He drives like a lunatic on the highway.</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Only a lunatic would swim in that freezing water.</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Special:FilePath/Person_in_CrazyFrog_costume_(from_cropped_PublicTransport_CrazyFrog).jpg?width=400</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>2</v>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L187"/>
+  <dimension ref="A1:L188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10717,8 +10717,59 @@
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>swanky</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>protzig, schick</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>/ˈswæŋki/</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Stylishly luxurious and expensive, often showing off wealth or status.</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>They had dinner at a swanky restaurant downtown.</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>He wore a swanky suit to the party.</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="n">
+        <v>2</v>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L188"/>
+  <dimension ref="A1:L189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10759,7 +10759,6 @@
           <t>He wore a swanky suit to the party.</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr"/>
       <c r="I188" t="n">
         <v>2</v>
       </c>
@@ -10768,8 +10767,63 @@
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Lighthouse</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Leuchtturm</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>/ˈlaɪthaʊs/</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>A tower with a bright light that guides ships at sea.</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>The lighthouse warned ships about the dangerous rocks.</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>We visited an old lighthouse by the coast.</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/a/a6/Aerial_photograph_60D_2012_05_13_8760_DxO_retusche.jpg</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>2</v>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L189"/>
+  <dimension ref="A1:L190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10822,10 +10822,65 @@
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
           <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Ferris wheel</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Riesenrad</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>/ˈferɪs wiːl/</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>A large rotating wheel with passenger cabins attached to its rim.</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>We rode the Ferris wheel at the carnival.</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>The Ferris wheel offers a great view of the city.</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/89/Ain_Dubai_View.jpg/1920px-Ain_Dubai_View.jpg</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>1</v>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>TV</t>
         </is>
       </c>
     </row>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L190"/>
+  <dimension ref="A1:L191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10877,8 +10877,59 @@
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>to stall</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>verzögern</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>/stɔːl/</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>To delay or stop making progress intentionally</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Stop stalling and answer my question.</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>The car engine stalled at the traffic light.</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="n">
+        <v>2</v>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
         <is>
           <t>TV</t>
         </is>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Vokabeln" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Fortschritt" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vokabeln" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fortschritt" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L191"/>
+  <dimension ref="A1:L291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10919,7 +10919,6 @@
           <t>The car engine stalled at the traffic light.</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr"/>
       <c r="I191" t="n">
         <v>2</v>
       </c>
@@ -10928,10 +10927,5409 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
           <t>TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>to reserve</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>reservieren</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>/rɪˈzɜːv/</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>To arrange for a table or seat to be kept for you.</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>I'd like to reserve a table for two at eight o'clock.</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>You should reserve early because the restaurant gets busy.</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Reservation</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Reservierung</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>/ˌrezəˈveɪʃn/</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>An arrangement to have a table or room kept for you.</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>We have a reservation under the name Becker.</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>The waiter checked our reservation and showed us to our seats.</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Speisekarte</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>/ˈmenjuː/</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>A list of the dishes available in a restaurant.</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Could we see the menu, please?</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>The menu had an English translation for tourists.</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Vorspeise</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>/ˈstɑːtə/</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>A small dish eaten before the main course.</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>For my starter I'll have the tomato soup.</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>The starters were so big we almost skipped the main course.</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Main course</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Hauptgericht</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>/ˌmeɪn ˈkɔːs/</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>The largest or most important dish of a meal.</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>What would you recommend as a main course?</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Her main course came with rice and grilled vegetables.</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Nachtisch</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>/dɪˈzɜːt/</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>A sweet dish eaten at the end of a meal.</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Would you like to see the dessert menu?</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>We were too full to order any dessert.</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Rechnung</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>/bɪl/</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>A piece of paper showing how much you owe for a meal.</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Could we have the bill, please?</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>He quietly paid the bill before anyone noticed.</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Trinkgeld</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>/tɪp/</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Extra money given to thank someone for good service.</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>We left a generous tip because the service was excellent.</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>In some countries a tip is already included in the bill.</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Waiter</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Kellner</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>/ˈweɪtə/</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>A person who serves food and drinks in a restaurant.</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>The waiter brought us some water and fresh bread.</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Our waiter was friendly and spoke a little German.</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>to order</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>bestellen</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>/ˈɔːdə/</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>To ask for food or drink in a restaurant.</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Are you ready to order, or do you need a few minutes?</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>I ordered the fish, but my friend chose the steak.</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Beverage</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Getränk</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>/ˈbevərɪdʒ/</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>A drink, especially one other than water.</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Hot beverages are served all day at the café.</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Would you like a beverage with your meal?</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Empfehlung</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>/ˌrekəmenˈdeɪʃn/</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>A suggestion that something is good or worth trying.</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>On the waiter's recommendation, we tried the local fish.</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Do you have any recommendations for a good restaurant nearby?</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>vegetarisch</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>/ˌvedʒəˈteəriən/</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Containing no meat or fish.</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Do you have any vegetarian dishes on the menu?</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>She has been vegetarian for almost ten years.</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Allergy</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Allergie</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>/ˈælədʒi/</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>A medical condition that makes you react badly to something.</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Please tell the waiter about any food allergy you have.</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>His nut allergy means he has to check every dish.</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Receipt</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Quittung</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>/rɪˈsiːt/</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>A paper proving that you have paid for something.</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Keep the receipt in case you want a refund.</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Could I have a receipt for my expenses, please?</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Cuisine</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>/kwɪˈziːn/</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>A style of cooking typical of a country or region.</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>We came here to taste the local cuisine.</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Italian cuisine is famous all over the world.</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>to split the bill</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>die Rechnung teilen</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>/splɪt ðə bɪl/</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Phrase</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>To divide the cost of a meal between people.</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Shall we split the bill evenly between the four of us?</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>They decided to split the bill rather than work out each share.</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Spezialität</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>/ˈspeʃəlti/</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>A dish a restaurant or region is especially known for.</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Grilled octopus is the specialty of this restaurant.</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Try the regional specialty — it's only made here.</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Booking</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Buchung</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>/ˈbʊkɪŋ/</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>An arrangement to use or have something at a later time.</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>I made a booking for three nights online.</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Our booking was confirmed by email within minutes.</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Course</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Gang</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>/kɔːs/</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>One separate part of a meal served at a time.</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>The set menu has four courses for a fixed price.</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>We took our time and enjoyed every course.</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>to check in</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>einchecken</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>/tʃek ɪn/</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>To register on arrival at a hotel or airport.</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>We can check in at the hotel after three o'clock.</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Please check in at least two hours before your flight.</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>to check out</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>auschecken</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>/tʃek aʊt/</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>To pay and leave a hotel at the end of your stay.</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>We have to check out before eleven in the morning.</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>She checked out early to catch the first train.</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Reception</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Rezeption</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>/rɪˈsepʃn/</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>The area in a hotel where guests arrive and get help.</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Leave your key at reception when you go out.</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>The reception is open twenty-four hours a day.</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Receptionist</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Empfangsmitarbeiter</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>/rɪˈsepʃənɪst/</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>A person who greets and helps guests at a hotel.</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>The receptionist gave us a map of the old town.</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Ask the receptionist if breakfast is included.</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>to book</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>buchen</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>/bʊk/</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>To arrange to have or use something later.</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>We booked a room with a sea view.</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>You can book the tour directly on their website.</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Vacancy</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>freies Zimmer</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>/ˈveɪkənsi/</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>A room that is available in a hotel.</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>The sign outside the hotel said there were no vacancies.</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Luckily the hotel still had a vacancy for one night.</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Double room</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Doppelzimmer</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>/ˌdʌbl ˈruːm/</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>A hotel room with a bed for two people.</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>We'd like to book a double room for the weekend.</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>The double room was small but very clean.</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Single room</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Einzelzimmer</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>/ˌsɪŋɡl ˈruːm/</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>A hotel room with a bed for one person.</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>A single room is cheaper than a double.</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>He always asks for a quiet single room.</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Luggage</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Gepäck</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>/ˈlʌɡɪdʒ/</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>The bags and cases you take when travelling.</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Can I leave my luggage here until check-in?</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>She packed all her luggage into one small suitcase.</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Suitcase</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Koffer</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>/ˈsuːtkeɪs/</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>A large bag with a handle for carrying clothes when travelling.</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>My suitcase was too heavy, so I had to repack it.</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>He dragged his suitcase up the stairs to the room.</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Backpack</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Rucksack</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>/ˈbækpæk/</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>A bag carried on your back, often used by travellers.</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>A backpack is easier to carry than a suitcase on the train.</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>She kept her passport in the front pocket of her backpack.</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>to unpack</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>auspacken</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>/ʌnˈpæk/</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>To take things out of a bag or case.</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Let's unpack before we go and explore the town.</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>He unpacked his clothes and hung them in the wardrobe.</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Wake-up call</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Weckruf</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>/ˈweɪk ʌp kɔːl/</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>A phone call from the hotel to wake you at a set time.</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Could I have a wake-up call at six tomorrow?</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>The wake-up call came right on time.</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Kaution</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>/dɪˈpɒzɪt/</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Money paid in advance that may be returned later.</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>The hotel asked for a small deposit at check-in.</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>You'll get your deposit back when you return the key.</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>/ˈlɒbi/</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>A large entrance hall in a hotel or public building.</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Let's meet in the lobby at nine in the morning.</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>The lobby had comfortable chairs and free coffee.</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Amenities</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Annehmlichkeiten</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>/əˈmiːnətiz/</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Useful or pleasant features that make a place comfortable.</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>The hotel offers amenities such as a pool and a gym.</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Free Wi-Fi is one of the amenities we always look for.</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Housekeeping</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Zimmerreinigung</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>/ˈhaʊskiːpɪŋ/</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>The hotel service that cleans the rooms.</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Housekeeping comes to clean the room every morning.</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Hang the sign on the door if you don't want housekeeping.</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Floor</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Stockwerk</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>/flɔː/</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>A level of a building.</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Our room is on the fourth floor with a great view.</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Take the lift to the top floor for the restaurant.</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Aussicht</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>/vjuː/</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>What you can see from a particular place.</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>The room has a beautiful view over the harbour.</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>We paid a little more for a room with a sea view.</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Departure</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Abflug</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>/dɪˈpɑːtʃə/</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>The act of leaving, especially of a plane or train.</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Our departure is delayed by half an hour.</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Check the board for the departure gate.</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Arrival</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Ankunft</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>/əˈraɪvl/</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>The act of reaching a place.</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Our arrival time is just after midnight.</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>On arrival, please go straight to passport control.</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Boarding pass</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Bordkarte</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>/ˈbɔːdɪŋ pɑːs/</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>A card that lets you get on a plane.</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Have your boarding pass and passport ready.</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>I saved my boarding pass on my phone.</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Flugsteig</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>/ɡeɪt/</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>The place in an airport where you get on a plane.</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Our flight leaves from gate twelve.</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>The gate has changed, so we have to hurry.</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Verspätung</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>/dɪˈleɪ/</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>A situation in which something happens later than planned.</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>There was a long delay because of the weather.</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>We missed our connection due to the delay.</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>to board</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>einsteigen</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>/bɔːd/</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>To get on a plane, train, ship or bus.</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Passengers can board the plane in ten minutes.</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>We boarded the ferry just before it left.</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Bahnsteig</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>/ˈplætfɔːm/</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>The area beside the track where you wait for a train.</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>The train to Rome leaves from platform three.</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>We ran along the platform to catch our train.</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Aisle seat</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Gangplatz</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>/ˈaɪl siːt/</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>A seat next to the passage on a plane or train.</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>I prefer an aisle seat so I can stretch my legs.</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>She asked to change her aisle seat for a window seat.</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Window seat</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Fensterplatz</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>/ˈwɪndəʊ siːt/</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>A seat next to the window on a plane or train.</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>The child wanted the window seat to watch the clouds.</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>From my window seat I could see the whole coast.</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Customs</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Zoll</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>/ˈkʌstəmz/</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>The place where officials check goods you bring into a country.</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>We had nothing to declare at customs.</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Customs officers checked our bags carefully.</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Passport</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Reisepass</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>/ˈpɑːspɔːt/</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>An official document that allows you to travel abroad.</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Don't forget your passport — we leave at dawn.</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>My passport expires next year, so I need a new one.</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Visum</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>/ˈviːzə/</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>An official mark allowing you to enter a country.</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>You need a visa to visit some countries.</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>We applied for our visa three weeks before the trip.</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Itinerary</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Reiseplan</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>/aɪˈtɪnərəri/</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>A detailed plan of a journey.</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Our itinerary includes three cities in five days.</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>She emailed me the full itinerary for the tour.</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Connection</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Anschluss</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>/kəˈnekʃn/</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>A train, bus or flight that lets you continue a journey.</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>We have a tight connection in Frankfurt.</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>If the first flight is late, we'll miss our connection.</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Round trip</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Hin- und Rückfahrt</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>/ˌraʊnd ˈtrɪp/</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>A journey to a place and back again.</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>A round trip is cheaper than two single tickets.</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>The round trip to the island takes about two hours.</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>to transfer</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>umsteigen</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>/trænsˈfɜː/</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>To change from one vehicle to another during a journey.</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>We have to transfer in London on the way home.</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Transfer to the blue line at the central station.</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Fare</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Fahrpreis</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>/feə/</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>The money you pay for a journey.</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>The bus fare into town is only two euros.</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Children travel at half the normal fare.</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Timetable</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Fahrplan</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>/ˈtaɪmteɪbl/</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>A list of the times when buses or trains arrive and leave.</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Check the timetable so we don't miss the last bus.</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>According to the timetable, the next train is at noon.</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Shuttle</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Zubringer</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>/ˈʃʌtl/</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>A bus or train that travels often between two places.</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>A free shuttle runs from the airport to the hotel.</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>We took the shuttle bus to the city centre.</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>to catch</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>erwischen</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>/kætʃ/</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>To get on a bus, train or plane before it leaves.</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>We need to hurry to catch the early train.</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>I just managed to catch the last ferry.</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>to miss</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>verpassen</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>/mɪs/</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>To fail to get on a bus, train or plane in time.</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>If we don't leave now, we'll miss the flight.</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>She missed her connection because of the delay.</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Rental car</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Mietwagen</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>/ˈrentl kɑː/</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>A car you pay to use for a period of time.</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>We picked up our rental car at the airport.</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>The rental car came with a full tank of fuel.</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Tour guide</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Reiseführer</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>/ˈtʊə ɡaɪd/</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>A person who shows tourists around a place.</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Our tour guide knew the history of every building.</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Ask the tour guide if we have time for photos.</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Guided tour</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Führung</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>/ˌɡaɪdɪd ˈtʊə/</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>An organised visit led by a guide.</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>We joined a guided tour of the old castle.</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>The guided tour lasts about ninety minutes.</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Landmark</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Wahrzeichen</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>/ˈlændmɑːk/</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>A famous building or feature that is easy to recognise.</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>The tower is the most famous landmark in the city.</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>We used the cathedral as a landmark to find our way.</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Sightseeing</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Besichtigung</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>/ˈsaɪtsiːɪŋ/</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>The activity of visiting interesting places as a tourist.</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>We spent the morning sightseeing in the old town.</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>After a day of sightseeing, my feet were aching.</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Souvenir</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Andenken</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>/ˌsuːvəˈnɪə/</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>An object you buy to remember a place or trip.</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>She bought a small souvenir for each of her friends.</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>This magnet is a cheap souvenir from our holiday.</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Admission</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Eintritt</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>/ədˈmɪʃn/</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>The money you pay to enter a place.</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Admission to the museum is free on Sundays.</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>The admission fee includes an audio guide.</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Brochure</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Broschüre</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>/ˈbrəʊʃə/</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>A small magazine with pictures and information.</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>I picked up a brochure about the local sights.</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>The brochure lists all the opening times.</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Währung</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>/ˈkʌrənsi/</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>The system of money used in a particular country.</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>What is the local currency in this country?</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>We changed some currency before leaving home.</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Exchange rate</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Wechselkurs</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>/ɪksˈtʃeɪndʒ reɪt/</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>How much one currency is worth in another.</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>The exchange rate is good for tourists this year.</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Check the exchange rate before you change money.</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>to exchange</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>umtauschen</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>/ɪksˈtʃeɪndʒ/</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>To change money from one currency into another.</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Where can I exchange euros for dollars?</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>We exchanged our cash at the bank, not the airport.</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Crowd</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Menschenmenge</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>/kraʊd/</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>A large number of people in one place.</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>A huge crowd gathered to watch the parade.</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>We lost each other in the crowd at the market.</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Viewpoint</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Aussichtspunkt</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>/ˈvjuːpɔɪnt/</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>A place from which you get a good view.</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>From the viewpoint you can see the whole valley.</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>We hiked up to a viewpoint to watch the sunset.</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Einheimischer</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>/ˈləʊkl/</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>A person who lives in a particular place.</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>The locals were friendly and gave us good tips.</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Eat where the locals eat to find the best food.</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Detour</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Umweg</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>/ˈdiːtʊə/</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>A longer route taken instead of the usual one.</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>We made a short detour to see the waterfall.</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>A detour added an hour to our journey.</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Highlight</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Höhepunkt</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>/ˈhaɪlaɪt/</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>The best or most enjoyable part of something.</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>The boat trip was the highlight of our holiday.</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>For me, the highlight was the old market square.</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>to explore</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>erkunden</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>/ɪkˈsplɔː/</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>To travel around a place to discover what it is like.</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>We spent the afternoon exploring the narrow streets.</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Let's explore the coast before the rain comes.</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Excursion</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Ausflug</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>/ɪkˈskɜːʃn/</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>A short trip made for pleasure.</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>We booked a day excursion to the nearby islands.</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>The hotel offers excursions to the mountains.</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Heritage</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Kulturerbe</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>/ˈherɪtɪdʒ/</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>The history and traditions of a place or people.</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>The old town is part of the country's heritage.</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>This site is protected as a world heritage location.</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Attraction</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Sehenswürdigkeit</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>/əˈtrækʃn/</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>A place that people visit for interest or pleasure.</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>The castle is the town's main attraction.</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Most attractions are within walking distance.</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Fest</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>/ˈfestɪvl/</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>A special event or celebration, often held every year.</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>We arrived during a colourful street festival.</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>The summer festival attracts visitors from all over.</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Sunscreen</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Sonnencreme</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>/ˈsʌnskriːn/</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>A cream that protects your skin from the sun.</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Don't forget to put on sunscreen at the beach.</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>I packed a high-factor sunscreen for the trip.</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Sunburn</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Sonnenbrand</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>/ˈsʌnbɜːn/</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Red, sore skin caused by too much sun.</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>He got a painful sunburn on the first day.</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Cover up to avoid sunburn around noon.</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Swimsuit</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Badeanzug</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>/ˈswɪmsuːt/</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>A piece of clothing worn for swimming.</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Pack your swimsuit — the hotel has a pool.</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>She bought a new swimsuit for the holiday.</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>to sunbathe</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>sonnenbaden</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>/ˈsʌnbeɪð/</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>To sit or lie in the sun to enjoy its warmth.</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>They spent the afternoon sunbathing by the sea.</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>I don't like to sunbathe for too long.</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Apotheke</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>/ˈfɑːməsi/</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>A shop where you can buy medicines.</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Is there a pharmacy near the hotel?</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>The pharmacy gave me something for my headache.</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Versicherung</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>/ɪnˈʃʊərəns/</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>An arrangement that protects you against loss or illness.</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Make sure you have travel insurance before you go.</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>The insurance covered the cost of the lost luggage.</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Emergency</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Notfall</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>/ɪˈmɜːdʒənsi/</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>A serious situation that needs immediate action.</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>In an emergency, call this number for help.</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>The hotel has a doctor on call for emergencies.</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Lost and found</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Fundbüro</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>/ˌlɒst ən ˈfaʊnd/</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>A place where lost items are kept until claimed.</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>I asked at the lost and found about my umbrella.</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>She found her camera at the station's lost and found.</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Directions</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Wegbeschreibung</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>/dəˈrekʃnz/</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Instructions on how to get to a place.</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Could you give me directions to the old harbour?</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>We asked a local for directions to the museum.</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>to get lost</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>sich verirren</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>/ɡet lɒst/</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Phrase</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>To no longer know where you are.</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>It's easy to get lost in these narrow streets.</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>We got lost twice before finding the restaurant.</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>nearby</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>in der Nähe</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>/ˌnɪəˈbaɪ/</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Adverb</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>A short distance away.</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Is there a supermarket nearby?</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>We found a lovely café nearby for breakfast.</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>crowded</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>überfüllt</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>/ˈkraʊdɪd/</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Full of people.</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>The beach was too crowded to find a free spot.</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>We avoided the crowded main square at midday.</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>affordable</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>erschwinglich</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>/əˈfɔːdəbl/</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Cheap enough that most people can pay for it.</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>We found an affordable hotel near the centre.</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>The set menu is tasty and affordable.</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>stunning</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>atemberaubend</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>/ˈstʌnɪŋ/</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Extremely beautiful or impressive.</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>The view from the cliff was absolutely stunning.</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>We watched a stunning sunset over the bay.</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>to haggle</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>feilschen</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>/ˈhæɡl/</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>To argue in order to agree on a lower price.</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>At the market you are expected to haggle a little.</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>He haggled with the seller and saved ten euros.</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Refund</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Rückerstattung</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>/ˈriːfʌnd/</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Money given back to you, for example for a cancelled trip.</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>We asked for a refund when the tour was cancelled.</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>The airline offered a full refund for the delay.</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>to recommend</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>empfehlen</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>/ˌrekəˈmend/</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>To suggest that something is good or worth trying.</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Can you recommend a good place for dinner?</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>I'd recommend visiting the market early in the morning.</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>to pack</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>packen</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>/pæk/</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>To put things into a bag or case for a journey.</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>I always pack light when I travel by plane.</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Did you pack the charger and the adapter?</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Reisen</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Adapter</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Adapter</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>/əˈdæptə/</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>A device that lets you use a plug in a foreign socket.</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Bring a travel adapter for your phone charger.</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>I forgot my adapter and couldn't charge my laptop.</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Reisen</t>
         </is>
       </c>
     </row>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L291"/>
+  <dimension ref="A1:M291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -557,6 +557,11 @@
           <t>Kategorie</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Beispielsatz DE</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -611,6 +616,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Sie ist sehr ehrgeizig und plant, vor ihrem 30. Geburtstag CEO zu werden.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -665,6 +675,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Sie ist unglaublich widerstandsfähig und hat sich innerhalb von Wochen erholt, nachdem sie ihren Job verloren hatte.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -723,6 +738,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Die Schmerzschwelle ist von Mensch zu Mensch sehr unterschiedlich.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -777,6 +797,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Ich neige dazu, Dinge aufzuschieben, wenn ich schwierige Aufgaben zu erledigen habe.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -831,6 +856,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Meinen besten Freund in diesem Café zu treffen, war ein reiner glücklicher Zufall.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -889,6 +919,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Wir müssen unsere Strategie verfeinern, bevor wir sie dem Vorstand präsentieren.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -943,6 +978,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Veränderung ist unvermeidlich – man kann den Fortschritt nicht aufhalten.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -1001,6 +1041,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Sie kämpfte damit, während der langen, langweiligen Besprechung wach zu bleiben.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1055,6 +1100,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Wissenschaftler erzielten letztes Jahr einen großen Durchbruch in der Krebsforschung.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1113,6 +1163,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Stell die Milch wieder in den Kühlschrank, wenn du sie benutzt hast.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1175,6 +1230,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Der Kühlschrank in der Küche macht seit Kurzem ein seltsames Geräusch.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -1233,6 +1293,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Sie füllte die Kaffeekanne und schaltete sie vor dem Frühstück ein.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1295,6 +1360,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Der Herd hat vier Kochplatten und einen großen Backofen darunter.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1353,6 +1423,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Stapel die schmutzigen Teller nach dem Essen in die Spülmaschine.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1411,6 +1486,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Ich habe für den Notfall immer eine Tüte tiefgefrorene Erbsen im Gefrierschrank.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -1469,6 +1549,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Setz den Wasserkocher auf – ich mache uns beiden eine Tasse Tee.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1527,6 +1612,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Heize den Backofen auf 200 °C vor, bevor du das Brot hineingibst.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -1589,6 +1679,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Sie stand am Herd und rührte vorsichtig die Suppe um.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1647,6 +1742,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Ich habe zwei Scheiben Brot zum Frühstück in den Toaster gesteckt.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -1705,6 +1805,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Ich habe eine volle Ladung Wäsche in die Waschmaschine gegeben.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -1767,6 +1872,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Brate die Würstchen zehn Minuten lang unter dem Grill.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -1825,6 +1935,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Benutz den Flaschenöffner an der Kühlschranktür, um dein Bier zu öffnen.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -1883,6 +1998,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Benutze beim Schneiden von Gemüse immer ein Schneidebrett, um die Arbeitsfläche zu schützen.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -1941,6 +2061,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Gib die gekochten Nudeln in das Sieb, um das Wasser abtropfen zu lassen.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -1999,6 +2124,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Hast du einen Korkenzieher? Ich würde gern diese Flasche Wein öffnen.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -2061,6 +2191,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Erhitze etwas Öl in der Bratpfanne, bevor du die Zwiebeln hinzugibst.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -2119,6 +2254,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Benutz die Reibe, um die Karotte für den Salat fein zu reiben.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -2181,6 +2321,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Reibe mit der Käsereibe etwas Parmesan über die Nudeln.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -2239,6 +2384,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Sie benutzt jeden Morgen einen elektrischen Entsafter, um frischen Orangensaft zu machen.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -2297,6 +2447,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Bedecke den Braten in der ersten Stunde des Garens mit Alufolie.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -2355,6 +2510,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Du brauchst eine Küchenwaage, um das Mehl genau abzuwiegen.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -2413,6 +2573,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Sie benutzte eine Schöpfkelle, um die Suppe in jede Schüssel zu füllen.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -2471,6 +2636,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Vermische Mehl, Eier und Milch in einer großen Rührschüssel.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -2529,6 +2699,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Benutz das Ofentuch, wenn du die Auflaufform aus dem Ofen nimmst.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -2583,6 +2758,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Zieh immer die Ofenhandschuhe an, bevor du in einen heißen Ofen greifst.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -2641,6 +2821,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Roll den Teig mit einem Nudelholz aus, bis er etwa 3 mm dick ist.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="42" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -2699,6 +2884,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Bring das Wasser in einem großen Kochtopf zum Kochen.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -2757,6 +2947,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Du brauchst einen Scheuerschwamm, um das angebrannte Essen von der Pfanne zu bekommen.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -2819,6 +3014,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Der Scheuerschwamm entfernte die angebrannten Reste vom Boden der Pfanne.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -2877,6 +3077,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Siebe das Mehl durch ein Sieb, um vor dem Backen alle Klümpchen zu entfernen.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -2939,6 +3144,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Ich brauche den Dosenöffner, um diese Dose Tomaten zu öffnen.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
@@ -3001,6 +3211,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Benutz die Zange, um die Steaks auf dem Grill zu wenden.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -3059,6 +3274,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Sie trug die Tassen Kaffee auf einem Tablett herein.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="42" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
@@ -3117,6 +3337,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Schlage die Eier, bis sie locker und schaumig sind.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -3175,6 +3400,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Rühre die Soße langsam mit einem Holzlöffel um, damit sie nicht anbrennt.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -3237,6 +3467,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Benutz ein scharfes Messer, um das Gemüse in gleichmäßige Stücke zu schneiden.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -3295,6 +3530,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Sie drehte die Spaghetti um ihre Gabel.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="42" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -3353,6 +3593,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Rühre deinen Kaffee mit einem Löffel um, damit sich der Zucker auflöst.</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -3407,6 +3652,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Sie aß die Mousse mit einem kleinen Dessertlöffel.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
@@ -3461,6 +3711,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Der Suppenlöffel wird rechts neben das übrige Besteck gelegt.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -3523,6 +3778,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Gib zwei Esslöffel Olivenöl in die Pfanne.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -3585,6 +3845,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Gib einen halben Teelöffel Salz in den Teig.</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -3643,6 +3908,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Er benutzte das Tranchiermesser, um das Brathähnchen am Tisch zu zerteilen.</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="42" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
@@ -3705,6 +3975,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Sie lernte auf ihrer Japanreise, Sushi mit Stäbchen zu essen.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -3763,6 +4038,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Sie machte sich eine Tasse Tee und setzte sich ans Fenster.</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
@@ -3821,6 +4101,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Sie schüttete die Cornflakes in eine Schüssel und gab etwas Milch dazu.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
@@ -3879,6 +4164,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Wir haben ein neues Geschirr-Set für das Esszimmer gekauft.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
@@ -3937,6 +4227,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Er goss den Orangensaft in ein hohes Glas.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -3995,6 +4290,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Sie öffnete ein neues Glas Erdnussbutter.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
@@ -4053,6 +4353,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Sie brachte einen Krug kaltes Wasser an den Tisch.</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -4111,6 +4416,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Er umfasste seine Tasse heiße Schokolade mit beiden Händen.</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
@@ -4169,6 +4479,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Sie stellte jedem Gast einen warmen Teller hin.</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -4223,6 +4538,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Sie stellte die Teetasse vorsichtig zurück auf ihre Untertasse.</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
@@ -4281,6 +4601,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Könntest du mir die Zuckerdose reichen? Ich möchte einen Löffel.</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -4339,6 +4664,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Sie ließ den Tee fünf Minuten in der Teekanne ziehen, bevor sie ihn eingoss.</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
@@ -4397,6 +4727,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Er goss den Rotwein in ein großes Weinglas.</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -4459,6 +4794,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Kratz die Reste in den Mülleimer und spül den Teller ab.</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
@@ -4517,6 +4857,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Decke die Schüssel mit Frischhaltefolie ab und stell sie über Nacht in den Kühlschrank.</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
@@ -4575,6 +4920,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Decke den Salat mit Frischhaltefolie ab, bevor du ihn in den Kühlschrank stellst.</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
@@ -4633,6 +4983,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Sie folgte dem Rezept Schritt für Schritt aus ihrem Lieblingskochbuch.</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -4687,6 +5042,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Wisch die Arbeitsfläche nach dem Kochen mit einem feuchten Spültuch ab.</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
@@ -4741,6 +5101,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Stapel das saubere Geschirr zum Trocknen auf dem Abtropfbrett.</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
@@ -4799,6 +5164,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Reiß ein Blatt Küchenrolle ab, um das Verschüttete aufzuwischen.</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="42" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
@@ -4853,6 +5223,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Steck den Stöpsel ins Waschbecken, bevor du es zum Abwaschen füllst.</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -4911,6 +5286,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Trockne die Gläser mit einem sauberen Geschirrtuch ab, damit sie keine Wasserflecken bekommen.</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="42" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
@@ -4969,6 +5349,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Die Gewürze stehen auf dem Regal über dem Herd.</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -5027,6 +5412,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Fülle das Spülbecken mit heißem Seifenwasser, um das Geschirr zu spülen.</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
@@ -5081,6 +5471,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Sie breitete eine saubere weiße Tischdecke über den Esstisch.</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -5139,6 +5534,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Gib etwas Spülmittel auf den Schwamm, bevor du die Töpfe schrubbst.</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="42" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
@@ -5193,6 +5593,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Wer spült heute Abend ab? Du bist dran.</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
@@ -5251,6 +5656,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Ich spüle ab, wenn du die Reste wegräumst.</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
@@ -5305,6 +5715,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Könntest du den Tisch abräumen, während ich den Nachtisch bringe?</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -5359,6 +5774,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Kannst du den Tisch decken? Das Essen ist in fünf Minuten fertig.</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
@@ -5417,6 +5837,11 @@
           <t>Kitchen/Cooking</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Würdest du den Tisch decken, während ich mit dem Kochen fertig werde?</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5469,6 +5894,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Die neue Richtlinie hatte erhebliche Auswirkungen auf die Mitarbeiterzufriedenheit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5521,6 +5951,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Es gab eine feine Veränderung in ihrem Ton, die alle aufmerken ließ.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5573,6 +6008,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Ihr Lächeln war echt – sie freute sich wirklich, ihn zu sehen.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5625,6 +6065,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Sie machte nach der Operation eine bemerkenswerte Genesung durch.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5677,6 +6122,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Er nimmt immer Rücksicht auf seine Nachbarn und hält den Lärm gering.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5729,6 +6179,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Trotz vieler Absagen blieb sie hartnäckig und bekam schließlich die Stelle.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5781,6 +6236,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Er war wegen der Prüfungsergebnisse ängstlich und konnte nicht schlafen.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5833,6 +6293,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Nach dem Marathon war sie völlig erschöpft und schlief sofort ein.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5885,6 +6350,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Ich war frustriert, dass das Internet während meiner Präsentation ständig ausfiel.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5937,6 +6407,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Er war erleichtert zu hören, dass sein Flug nicht gestrichen wurde.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5989,6 +6464,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Nach seinem Witz entstand ein unangenehmes Schweigen.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6041,6 +6521,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Das Hotel war in Ordnung – nichts Besonderes, aber sauber und gemütlich.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6093,6 +6578,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Sie hatte einen lebhaften Traum, in dem sie über die Berge flog.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6145,6 +6635,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Der Roman hatte eine fesselnde Handlung, die mich die ganze Nacht weiterlesen ließ.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6197,6 +6692,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Ich bin wirklich dankbar für all die Hilfe, die du mir gegeben hast.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6249,6 +6749,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Er war zynisch, was das Einhalten von Versprechen durch Politiker anging.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6301,6 +6806,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Sie war vorsichtig, als sie die vereiste Straße überquerte.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6353,6 +6863,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Die Vorstellung war mittelmäßig – das Publikum hatte viel mehr erwartet.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6405,6 +6920,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Es war eine mutige Entscheidung, ihren Job zu kündigen und ihr eigenes Unternehmen zu gründen.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6457,6 +6977,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Die Resonanz auf den Spendenaufruf war überwältigend – Tausende spendeten.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6509,6 +7034,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Sie arbeitete hart, um ihren Traum zu verwirklichen, Ärztin zu werden.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6561,6 +7091,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Er brauchte eine Weile, um sich an das neue Arbeitsumfeld anzupassen.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6613,6 +7148,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Ich schätze wirklich alles, was du getan hast, um mir zu helfen.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6665,6 +7205,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Geh nicht davon aus, dass alle deine Meinung teilen – frag erst nach.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6717,6 +7262,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Versuche zu vermeiden, zu viel Zucker zu essen, wenn du gesund bleiben willst.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6769,6 +7319,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Der neue Geschäftsführer stellte die Art und Weise infrage, wie das Unternehmen die Dinge immer gemacht hatte.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6821,6 +7376,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Er überzeugte seinen Chef, dem Team einen zusätzlichen freien Tag zu geben.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6873,6 +7433,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Die Arbeiter forderten bessere Bezahlung und Arbeitsbedingungen.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6925,6 +7490,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Die Lehrerin betonte, wie wichtig es ist, jeden Tag zu lesen.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6977,6 +7547,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Seine Eltern ermutigten ihn immer, seiner Leidenschaft für Musik nachzugehen.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7029,6 +7604,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Sie zögerte, bevor sie die schwierige Frage beantwortete.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7081,6 +7661,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Sein Lehrer beeinflusste ihn, Architektur zu studieren.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7133,6 +7718,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Sie handelten ein besseres Angebot aus, indem sie ruhig und vorbereitet blieben.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7185,6 +7775,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Sie überwand ihre Angst vor dem öffentlichen Reden, nachdem sie einer Theatergruppe beigetreten war.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7237,6 +7832,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Sie beschloss, eine Karriere im Journalismus zu verfolgen.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7289,6 +7889,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Ich erkannte sie sofort, obwohl ich sie zehn Jahre lang nicht gesehen hatte.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7341,6 +7946,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Du kannst dich immer auf sie verlassen, dass sie die Arbeit pünktlich erledigt.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7393,6 +8003,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Die Dokumentation enthüllte schockierende Fakten über die Lebensmittelindustrie.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7445,6 +8060,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Ich vermute, dass er den Bericht nicht rechtzeitig fertiggestellt hat.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7497,6 +8117,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Sie wurde vom Küchenfenster aus Zeugin des Unfalls.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7549,6 +8174,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Die Meisterschaft zu gewinnen war die größte Leistung seiner Karriere.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7601,6 +8231,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Wir brauchen einen neuen Ansatz, um dieses seit Langem bestehende Problem zu lösen.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7653,6 +8288,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Er brachte ein überzeugendes Argument für die Änderung der Unternehmensrichtlinie vor.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7705,6 +8345,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Ihre positive Einstellung half dem Team, in schwierigen Zeiten motiviert zu bleiben.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7757,6 +8402,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Ins Ausland zu ziehen war die größte Herausforderung, der sie je begegnet war.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7809,6 +8459,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Angesichts der Umstände meisterte sie die Krise außerordentlich gut.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7861,6 +8516,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Sein Engagement für das Projekt war vom ersten Tag an erkennbar.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7913,6 +8573,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Sicherheit ist auf jeder Baustelle unser größtes Anliegen.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7965,6 +8630,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Der Konflikt zwischen den beiden Abteilungen bremste alles aus.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8017,6 +8687,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Er lernte nicht und fiel infolgedessen durch die Prüfung.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8069,6 +8744,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Du musst den ganzen Artikel lesen, um den Kontext des Zitats zu verstehen.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8121,6 +8801,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Sie stand vor einem Dilemma: den besser bezahlten Job annehmen oder näher bei der Familie bleiben.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8173,6 +8858,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Die Polizei fand keine Beweise, die ihn mit dem Verbrechen in Verbindung brachten.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8225,6 +8915,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Er sah jeden Misserfolg als Lernchance, nicht als Rückschlag.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8277,6 +8972,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Sie entwickelte die Gewohnheit, vor dem Schlafengehen zu lesen, um abzuschalten.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8329,6 +9029,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Das neue Gesetz hatte große Auswirkungen auf kleine Unternehmen.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8381,6 +9086,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Seine Absicht war, sich zu entschuldigen, aber er fand nie den richtigen Moment.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8433,6 +9143,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Dieses Jobangebot ist eine fantastische Gelegenheit, die sie sich nicht entgehen lassen sollte.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8485,6 +9200,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Reisen ins Ausland gab ihr eine völlig neue Sicht auf das Leben.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8537,6 +9257,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Gesundheit sollte immer deine oberste Priorität sein.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8589,6 +9314,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Als Elternteil hast du die Verantwortung, deine Kinder zu beschützen.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8641,6 +9371,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Harte Arbeit sollte mit einer fairen Belohnung honoriert werden.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8693,6 +9428,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Ein Unternehmen zu gründen ist immer mit einem gewissen Risiko verbunden.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8745,6 +9485,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Wir müssen eine langfristige Lösung für das Verkehrsproblem finden.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8797,6 +9542,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Das Unternehmen braucht eine klare Strategie, um auf dem Weltmarkt zu bestehen.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8849,6 +9599,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Der Kampf, Beruf und Familie unter einen Hut zu bringen, ist etwas, das viele Menschen teilen.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8901,6 +9656,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Vertrauen ist die Grundlage jeder gesunden Beziehung.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8953,6 +9713,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Die wirtschaftliche Unsicherheit machte Investoren zögerlich, große Summen zu investieren.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9005,6 +9770,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Die Kampagne soll das Bewusstsein für psychische Gesundheit schärfen.</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9057,6 +9827,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Nach dem Streit gab es eine sichtbare Spannung zwischen den beiden Kollegen.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9109,6 +9884,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Anfangs konnte ich nicht herausfinden, wie man die neue Software benutzt.</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9161,6 +9941,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Gib nicht auf – du bist fast am Ziel!</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9213,6 +9998,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Ich freue mich schon sehr auf unseren Urlaub nächste Woche.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9265,6 +10055,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Ihr leuchtend gelber Mantel ließ sie in der Menge hervorstechen.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9317,6 +10112,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Er verpasste drei Wochen Schule und brauchte Zeit, um den Stoff nachzuholen.</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9369,6 +10169,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Hör auf, den Zahnarzttermin aufzuschieben – buch ihn einfach!</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9421,6 +10226,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Beim Aufräumen des Dachbodens stieß ich auf ein altes Fotoalbum.</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9473,6 +10283,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Hast du dich entschieden, an welcher Universität du dich bewerben willst?</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9525,6 +10340,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Denk daran, dass die Frist am Freitag ist, nicht am Montag.</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9577,6 +10397,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Nimm deine Gesundheit nicht als selbstverständlich hin – pass auf dich auf.</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -9629,6 +10454,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Uns ist die Milch ausgegangen, also muss ich zum Laden gehen.</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9681,6 +10511,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Sie kommt mit all ihren Kollegen wirklich gut aus.</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9733,6 +10568,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Sie wies auf mehrere Fehler im Bericht hin, bevor er eingereicht wurde.</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9785,6 +10625,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Er brachte das Thema Überstundenbezahlung in der Teambesprechung zur Sprache.</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9837,6 +10682,11 @@
           <t>Allgemein</t>
         </is>
       </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Mach weiter so – du machst das großartig!</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9889,6 +10739,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Der Regisseur baut die Spannung im gesamten ersten Akt langsam auf.</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9941,6 +10796,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Niemand sah die überraschende Wendung kommen – sie veränderte die Geschichte völlig.</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9993,6 +10853,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Die Staffel endete mit einem Cliffhanger – wir haben keine Ahnung, ob sie überlebt hat.</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10045,6 +10910,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Der Protagonist der Serie ist ein Ermittler mit einer schwierigen Vergangenheit.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10097,6 +10967,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Der Antagonist war so gut geschrieben, dass das Publikum fast mit ihm sympathisierte.</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10149,6 +11024,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Die Folge verwendet eine Rückblende, um die schwierige Kindheit der Figur zu erklären.</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10201,6 +11081,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Die unheilvolle Musik in der Eröffnungsszene war eine klare Vorausdeutung.</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10253,6 +11138,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Achtung: Der nächste Absatz enthält Spoiler zur neuesten Folge.</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10305,6 +11195,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Wir haben die ganze Serie über das lange Wochenende am Stück durchgeschaut.</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10357,6 +11252,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Das Staffelfinale ließ Millionen Fans sehnsüchtig auf die nächste Staffel warten.</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10409,6 +11309,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Die romantische Nebenhandlung verlieh dem Actionfilm Tiefe und Wärme.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -10461,6 +11366,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Die Charakterentwicklung der Serie ist das, was die Zuschauer immer wieder zurückkommen lässt.</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -10513,6 +11423,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Die Erzählweise des Films springt zwischen drei verschiedenen Zeitebenen hin und her.</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -10565,6 +11480,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Krimidrama ist ihr Lieblingsgenre – sie wird es nie müde.</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10617,6 +11537,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Sie verbrachte drei Jahre damit, das Drehbuch für ihren Debütfilm zu schreiben.</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -10814,8 +11739,10 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/a/a6/Aerial_photograph_60D_2012_05_13_8760_DxO_retusche.jpg</t>
         </is>
       </c>
-      <c r="I189" t="n">
-        <v>2</v>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -10825,6 +11752,11 @@
       <c r="L189" t="inlineStr">
         <is>
           <t>Allgemein</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Der Leuchtturm warnte Schiffe vor den gefährlichen Felsen.</t>
         </is>
       </c>
     </row>
@@ -10869,8 +11801,10 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/89/Ain_Dubai_View.jpg/1920px-Ain_Dubai_View.jpg</t>
         </is>
       </c>
-      <c r="I190" t="n">
-        <v>1</v>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -10880,6 +11814,11 @@
       <c r="L190" t="inlineStr">
         <is>
           <t>TV</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Wir fuhren auf dem Riesenrad auf dem Jahrmarkt.</t>
         </is>
       </c>
     </row>
@@ -10919,8 +11858,10 @@
           <t>The car engine stalled at the traffic light.</t>
         </is>
       </c>
-      <c r="I191" t="n">
-        <v>2</v>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -10930,6 +11871,11 @@
       <c r="L191" t="inlineStr">
         <is>
           <t>TV</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>Hör auf hinzuhalten und beantworte meine Frage.</t>
         </is>
       </c>
     </row>
@@ -10969,7 +11915,6 @@
           <t>You should reserve early because the restaurant gets busy.</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
           <t>B1</t>
@@ -10980,10 +11925,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Ich möchte einen Tisch für zwei Personen um acht Uhr reservieren.</t>
         </is>
       </c>
     </row>
@@ -11023,7 +11972,6 @@
           <t>The waiter checked our reservation and showed us to our seats.</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>B1</t>
@@ -11034,10 +11982,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Wir haben eine Reservierung auf den Namen Becker.</t>
         </is>
       </c>
     </row>
@@ -11077,7 +12029,6 @@
           <t>The menu had an English translation for tourists.</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
           <t>A2</t>
@@ -11088,10 +12039,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Könnten wir bitte die Speisekarte sehen?</t>
         </is>
       </c>
     </row>
@@ -11131,7 +12086,6 @@
           <t>The starters were so big we almost skipped the main course.</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
           <t>B1</t>
@@ -11142,10 +12096,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>Als Vorspeise nehme ich die Tomatensuppe.</t>
         </is>
       </c>
     </row>
@@ -11185,7 +12143,6 @@
           <t>Her main course came with rice and grilled vegetables.</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
           <t>B1</t>
@@ -11196,10 +12153,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Was würden Sie als Hauptgericht empfehlen?</t>
         </is>
       </c>
     </row>
@@ -11239,7 +12200,6 @@
           <t>We were too full to order any dessert.</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>A2</t>
@@ -11250,10 +12210,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>Möchten Sie die Dessertkarte sehen?</t>
         </is>
       </c>
     </row>
@@ -11293,7 +12257,6 @@
           <t>He quietly paid the bill before anyone noticed.</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
           <t>A2</t>
@@ -11304,10 +12267,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Könnten wir bitte die Rechnung haben?</t>
         </is>
       </c>
     </row>
@@ -11347,7 +12314,6 @@
           <t>In some countries a tip is already included in the bill.</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>B1</t>
@@ -11358,10 +12324,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Wir gaben ein großzügiges Trinkgeld, weil der Service ausgezeichnet war.</t>
         </is>
       </c>
     </row>
@@ -11401,7 +12371,6 @@
           <t>Our waiter was friendly and spoke a little German.</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>A2</t>
@@ -11412,10 +12381,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Der Kellner brachte uns Wasser und frisches Brot.</t>
         </is>
       </c>
     </row>
@@ -11455,7 +12428,6 @@
           <t>I ordered the fish, but my friend chose the steak.</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
           <t>A2</t>
@@ -11466,10 +12438,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>Möchten Sie bestellen, oder brauchen Sie noch ein paar Minuten?</t>
         </is>
       </c>
     </row>
@@ -11509,7 +12485,6 @@
           <t>Would you like a beverage with your meal?</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
           <t>B1</t>
@@ -11520,10 +12495,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>Im Café werden den ganzen Tag über Heißgetränke serviert.</t>
         </is>
       </c>
     </row>
@@ -11563,7 +12542,6 @@
           <t>Do you have any recommendations for a good restaurant nearby?</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
           <t>B1</t>
@@ -11574,10 +12552,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>Auf Empfehlung des Kellners probierten wir den heimischen Fisch.</t>
         </is>
       </c>
     </row>
@@ -11617,7 +12599,6 @@
           <t>She has been vegetarian for almost ten years.</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>B1</t>
@@ -11628,10 +12609,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Haben Sie vegetarische Gerichte auf der Speisekarte?</t>
         </is>
       </c>
     </row>
@@ -11671,7 +12656,6 @@
           <t>His nut allergy means he has to check every dish.</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
           <t>B1</t>
@@ -11682,10 +12666,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>Bitte teilen Sie dem Kellner mit, ob Sie eine Lebensmittelallergie haben.</t>
         </is>
       </c>
     </row>
@@ -11725,7 +12713,6 @@
           <t>Could I have a receipt for my expenses, please?</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
           <t>B1</t>
@@ -11736,10 +12723,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>Bewahren Sie die Quittung auf, falls Sie eine Rückerstattung möchten.</t>
         </is>
       </c>
     </row>
@@ -11779,7 +12770,6 @@
           <t>Italian cuisine is famous all over the world.</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
           <t>B1</t>
@@ -11790,10 +12780,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Wir sind hierhergekommen, um die regionale Küche zu probieren.</t>
         </is>
       </c>
     </row>
@@ -11833,7 +12827,6 @@
           <t>They decided to split the bill rather than work out each share.</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
           <t>B1</t>
@@ -11844,10 +12837,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>Sollen wir die Rechnung gleichmäßig zwischen uns vieren teilen?</t>
         </is>
       </c>
     </row>
@@ -11887,7 +12884,6 @@
           <t>Try the regional specialty — it's only made here.</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
           <t>B1</t>
@@ -11898,10 +12894,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>Gegrillter Oktopus ist die Spezialität dieses Restaurants.</t>
         </is>
       </c>
     </row>
@@ -11941,7 +12941,6 @@
           <t>Our booking was confirmed by email within minutes.</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
           <t>B1</t>
@@ -11952,10 +12951,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>Ich habe online eine Buchung für drei Nächte vorgenommen.</t>
         </is>
       </c>
     </row>
@@ -11995,7 +12998,6 @@
           <t>We took our time and enjoyed every course.</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
           <t>B1</t>
@@ -12006,10 +13008,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>Das Menü hat vier Gänge zu einem Festpreis.</t>
         </is>
       </c>
     </row>
@@ -12049,7 +13055,6 @@
           <t>Please check in at least two hours before your flight.</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
           <t>B1</t>
@@ -12060,10 +13065,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>Wir können nach drei Uhr im Hotel einchecken.</t>
         </is>
       </c>
     </row>
@@ -12103,7 +13112,6 @@
           <t>She checked out early to catch the first train.</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
           <t>B1</t>
@@ -12114,10 +13122,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>Wir müssen vor elf Uhr morgens auschecken.</t>
         </is>
       </c>
     </row>
@@ -12157,7 +13169,6 @@
           <t>The reception is open twenty-four hours a day.</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
           <t>B1</t>
@@ -12168,10 +13179,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>Geben Sie Ihren Schlüssel an der Rezeption ab, wenn Sie ausgehen.</t>
         </is>
       </c>
     </row>
@@ -12211,7 +13226,6 @@
           <t>Ask the receptionist if breakfast is included.</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
           <t>B1</t>
@@ -12222,10 +13236,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Der Empfangsmitarbeiter gab uns einen Stadtplan der Altstadt.</t>
         </is>
       </c>
     </row>
@@ -12265,7 +13283,6 @@
           <t>You can book the tour directly on their website.</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
           <t>A2</t>
@@ -12276,10 +13293,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Wir haben ein Zimmer mit Meerblick gebucht.</t>
         </is>
       </c>
     </row>
@@ -12319,7 +13340,6 @@
           <t>Luckily the hotel still had a vacancy for one night.</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
           <t>B2</t>
@@ -12330,10 +13350,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Das Schild draußen wies darauf hin, dass keine Zimmer mehr frei waren.</t>
         </is>
       </c>
     </row>
@@ -12373,7 +13397,6 @@
           <t>The double room was small but very clean.</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr">
         <is>
           <t>B1</t>
@@ -12384,10 +13407,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Wir möchten ein Doppelzimmer für das Wochenende buchen.</t>
         </is>
       </c>
     </row>
@@ -12427,7 +13454,6 @@
           <t>He always asks for a quiet single room.</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
           <t>B1</t>
@@ -12438,10 +13464,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>Ein Einzelzimmer ist günstiger als ein Doppelzimmer.</t>
         </is>
       </c>
     </row>
@@ -12481,7 +13511,6 @@
           <t>She packed all her luggage into one small suitcase.</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
           <t>B1</t>
@@ -12492,10 +13521,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>Kann ich mein Gepäck bis zum Check-in hier lassen?</t>
         </is>
       </c>
     </row>
@@ -12535,7 +13568,6 @@
           <t>He dragged his suitcase up the stairs to the room.</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr">
         <is>
           <t>A2</t>
@@ -12546,10 +13578,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>Mein Koffer war zu schwer, also musste ich ihn neu packen.</t>
         </is>
       </c>
     </row>
@@ -12589,7 +13625,6 @@
           <t>She kept her passport in the front pocket of her backpack.</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
           <t>A2</t>
@@ -12600,10 +13635,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>Ein Rucksack lässt sich im Zug leichter tragen als ein Koffer.</t>
         </is>
       </c>
     </row>
@@ -12643,7 +13682,6 @@
           <t>He unpacked his clothes and hung them in the wardrobe.</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
           <t>B1</t>
@@ -12654,10 +13692,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>Lass uns auspacken, bevor wir die Stadt erkunden gehen.</t>
         </is>
       </c>
     </row>
@@ -12697,7 +13739,6 @@
           <t>The wake-up call came right on time.</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
           <t>B2</t>
@@ -12708,10 +13749,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>Könnte ich morgen um sechs Uhr einen Weckruf bekommen?</t>
         </is>
       </c>
     </row>
@@ -12751,7 +13796,6 @@
           <t>You'll get your deposit back when you return the key.</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr">
         <is>
           <t>B1</t>
@@ -12762,10 +13806,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>Das Hotel verlangte beim Check-in eine kleine Kaution.</t>
         </is>
       </c>
     </row>
@@ -12805,7 +13853,6 @@
           <t>The lobby had comfortable chairs and free coffee.</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
           <t>B1</t>
@@ -12816,10 +13863,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>Treffen wir uns morgens um neun in der Lobby.</t>
         </is>
       </c>
     </row>
@@ -12859,7 +13910,6 @@
           <t>Free Wi-Fi is one of the amenities we always look for.</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
           <t>B2</t>
@@ -12870,10 +13920,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>Das Hotel bietet Annehmlichkeiten wie einen Pool und ein Fitnessstudio.</t>
         </is>
       </c>
     </row>
@@ -12913,7 +13967,6 @@
           <t>Hang the sign on the door if you don't want housekeeping.</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
           <t>B2</t>
@@ -12924,10 +13977,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>Die Zimmerreinigung kommt jeden Morgen, um das Zimmer zu putzen.</t>
         </is>
       </c>
     </row>
@@ -12967,7 +14024,6 @@
           <t>Take the lift to the top floor for the restaurant.</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
           <t>A2</t>
@@ -12978,10 +14034,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>Unser Zimmer ist im vierten Stockwerk mit einer tollen Aussicht.</t>
         </is>
       </c>
     </row>
@@ -13021,7 +14081,6 @@
           <t>We paid a little more for a room with a sea view.</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
           <t>A2</t>
@@ -13032,10 +14091,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>Das Zimmer hat eine schöne Aussicht über den Hafen.</t>
         </is>
       </c>
     </row>
@@ -13075,7 +14138,6 @@
           <t>Check the board for the departure gate.</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
           <t>B1</t>
@@ -13086,10 +14148,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>Unser Abflug verspätet sich um eine halbe Stunde.</t>
         </is>
       </c>
     </row>
@@ -13129,7 +14195,6 @@
           <t>On arrival, please go straight to passport control.</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr">
         <is>
           <t>B1</t>
@@ -13140,10 +14205,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>Unsere Ankunftszeit ist kurz nach Mitternacht.</t>
         </is>
       </c>
     </row>
@@ -13183,7 +14252,6 @@
           <t>I saved my boarding pass on my phone.</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr">
         <is>
           <t>B1</t>
@@ -13194,10 +14262,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>Halten Sie Ihre Bordkarte und Ihren Reisepass bereit.</t>
         </is>
       </c>
     </row>
@@ -13237,7 +14309,6 @@
           <t>The gate has changed, so we have to hurry.</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr">
         <is>
           <t>A2</t>
@@ -13248,10 +14319,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Unser Flug geht von Flugsteig zwölf ab.</t>
         </is>
       </c>
     </row>
@@ -13291,7 +14366,6 @@
           <t>We missed our connection due to the delay.</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr">
         <is>
           <t>B1</t>
@@ -13302,10 +14376,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Wegen des Wetters gab es eine lange Verspätung.</t>
         </is>
       </c>
     </row>
@@ -13345,7 +14423,6 @@
           <t>We boarded the ferry just before it left.</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr">
         <is>
           <t>B1</t>
@@ -13356,10 +14433,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>Die Passagiere können in zehn Minuten in das Flugzeug einsteigen.</t>
         </is>
       </c>
     </row>
@@ -13399,7 +14480,6 @@
           <t>We ran along the platform to catch our train.</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr">
         <is>
           <t>B1</t>
@@ -13410,10 +14490,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>Der Zug nach Rom fährt von Bahnsteig drei ab.</t>
         </is>
       </c>
     </row>
@@ -13453,7 +14537,6 @@
           <t>She asked to change her aisle seat for a window seat.</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr">
         <is>
           <t>B2</t>
@@ -13464,10 +14547,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>Ich bevorzuge einen Gangplatz, damit ich meine Beine ausstrecken kann.</t>
         </is>
       </c>
     </row>
@@ -13507,7 +14594,6 @@
           <t>From my window seat I could see the whole coast.</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr">
         <is>
           <t>B1</t>
@@ -13518,10 +14604,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>Das Kind wollte den Fensterplatz, um die Wolken zu beobachten.</t>
         </is>
       </c>
     </row>
@@ -13561,7 +14651,6 @@
           <t>Customs officers checked our bags carefully.</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr">
         <is>
           <t>B2</t>
@@ -13572,10 +14661,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>Wir hatten am Zoll nichts zu verzollen.</t>
         </is>
       </c>
     </row>
@@ -13615,7 +14708,6 @@
           <t>My passport expires next year, so I need a new one.</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr">
         <is>
           <t>A2</t>
@@ -13626,10 +14718,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>Vergiss deinen Reisepass nicht – wir fahren im Morgengrauen los.</t>
         </is>
       </c>
     </row>
@@ -13669,7 +14765,6 @@
           <t>We applied for our visa three weeks before the trip.</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr">
         <is>
           <t>B1</t>
@@ -13680,10 +14775,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>Für manche Länder braucht man ein Visum.</t>
         </is>
       </c>
     </row>
@@ -13723,7 +14822,6 @@
           <t>She emailed me the full itinerary for the tour.</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr">
         <is>
           <t>B2</t>
@@ -13734,10 +14832,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>Unser Reiseplan umfasst drei Städte in fünf Tagen.</t>
         </is>
       </c>
     </row>
@@ -13777,7 +14879,6 @@
           <t>If the first flight is late, we'll miss our connection.</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr">
         <is>
           <t>B1</t>
@@ -13788,10 +14889,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>Wir haben einen knappen Anschluss in Frankfurt.</t>
         </is>
       </c>
     </row>
@@ -13831,7 +14936,6 @@
           <t>The round trip to the island takes about two hours.</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr">
         <is>
           <t>B1</t>
@@ -13842,10 +14946,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>Eine Hin- und Rückfahrt ist günstiger als zwei Einzeltickets.</t>
         </is>
       </c>
     </row>
@@ -13885,7 +14993,6 @@
           <t>Transfer to the blue line at the central station.</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr">
         <is>
           <t>B1</t>
@@ -13896,10 +15003,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>Auf dem Heimweg müssen wir in London umsteigen.</t>
         </is>
       </c>
     </row>
@@ -13939,7 +15050,6 @@
           <t>Children travel at half the normal fare.</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr">
         <is>
           <t>B1</t>
@@ -13950,10 +15060,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Der Busfahrpreis in die Stadt beträgt nur zwei Euro.</t>
         </is>
       </c>
     </row>
@@ -13993,7 +15107,6 @@
           <t>According to the timetable, the next train is at noon.</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr">
         <is>
           <t>B1</t>
@@ -14004,10 +15117,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>Schau auf den Fahrplan, damit wir den letzten Bus nicht verpassen.</t>
         </is>
       </c>
     </row>
@@ -14047,7 +15164,6 @@
           <t>We took the shuttle bus to the city centre.</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr">
         <is>
           <t>B1</t>
@@ -14058,10 +15174,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Ein kostenloser Zubringer fährt vom Flughafen zum Hotel.</t>
         </is>
       </c>
     </row>
@@ -14101,7 +15221,6 @@
           <t>I just managed to catch the last ferry.</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr">
         <is>
           <t>A2</t>
@@ -14112,10 +15231,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>Wir müssen uns beeilen, um den frühen Zug zu erwischen.</t>
         </is>
       </c>
     </row>
@@ -14155,7 +15278,6 @@
           <t>She missed her connection because of the delay.</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr">
         <is>
           <t>A2</t>
@@ -14166,10 +15288,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>Wenn wir jetzt nicht losgehen, verpassen wir den Flug.</t>
         </is>
       </c>
     </row>
@@ -14209,7 +15335,6 @@
           <t>The rental car came with a full tank of fuel.</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr">
         <is>
           <t>B1</t>
@@ -14220,10 +15345,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>Wir holten unseren Mietwagen am Flughafen ab.</t>
         </is>
       </c>
     </row>
@@ -14263,7 +15392,6 @@
           <t>Ask the tour guide if we have time for photos.</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
         <is>
           <t>B1</t>
@@ -14274,10 +15402,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>Unser Reiseführer kannte die Geschichte jedes Gebäudes.</t>
         </is>
       </c>
     </row>
@@ -14317,7 +15449,6 @@
           <t>The guided tour lasts about ninety minutes.</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr">
         <is>
           <t>B1</t>
@@ -14328,10 +15459,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>Wir nahmen an einer Führung durch das alte Schloss teil.</t>
         </is>
       </c>
     </row>
@@ -14371,7 +15506,6 @@
           <t>We used the cathedral as a landmark to find our way.</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr">
         <is>
           <t>B1</t>
@@ -14382,10 +15516,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>Der Turm ist das berühmteste Wahrzeichen der Stadt.</t>
         </is>
       </c>
     </row>
@@ -14425,7 +15563,6 @@
           <t>After a day of sightseeing, my feet were aching.</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr">
         <is>
           <t>B1</t>
@@ -14436,10 +15573,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>Wir verbrachten den Vormittag mit der Besichtigung der Altstadt.</t>
         </is>
       </c>
     </row>
@@ -14479,7 +15620,6 @@
           <t>This magnet is a cheap souvenir from our holiday.</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr">
         <is>
           <t>B1</t>
@@ -14490,10 +15630,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>Sie kaufte für jede ihrer Freundinnen ein kleines Andenken.</t>
         </is>
       </c>
     </row>
@@ -14533,7 +15677,6 @@
           <t>The admission fee includes an audio guide.</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr">
         <is>
           <t>B1</t>
@@ -14544,10 +15687,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>Der Eintritt ins Museum ist sonntags frei.</t>
         </is>
       </c>
     </row>
@@ -14587,7 +15734,6 @@
           <t>The brochure lists all the opening times.</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr">
         <is>
           <t>B1</t>
@@ -14598,10 +15744,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>Ich nahm eine Broschüre über die örtlichen Sehenswürdigkeiten mit.</t>
         </is>
       </c>
     </row>
@@ -14641,7 +15791,6 @@
           <t>We changed some currency before leaving home.</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr">
         <is>
           <t>B1</t>
@@ -14652,10 +15801,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>Was ist die Landeswährung in diesem Land?</t>
         </is>
       </c>
     </row>
@@ -14695,7 +15848,6 @@
           <t>Check the exchange rate before you change money.</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr">
         <is>
           <t>B2</t>
@@ -14706,10 +15858,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>Der Wechselkurs ist dieses Jahr gut für Touristen.</t>
         </is>
       </c>
     </row>
@@ -14749,7 +15905,6 @@
           <t>We exchanged our cash at the bank, not the airport.</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr">
         <is>
           <t>B1</t>
@@ -14760,10 +15915,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>Wo kann ich Euro in Dollar umtauschen?</t>
         </is>
       </c>
     </row>
@@ -14803,7 +15962,6 @@
           <t>We lost each other in the crowd at the market.</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr">
         <is>
           <t>B1</t>
@@ -14814,10 +15972,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>Eine riesige Menschenmenge versammelte sich, um die Parade zu sehen.</t>
         </is>
       </c>
     </row>
@@ -14857,7 +16019,6 @@
           <t>We hiked up to a viewpoint to watch the sunset.</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr">
         <is>
           <t>B1</t>
@@ -14868,10 +16029,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>Vom Aussichtspunkt aus kann man das ganze Tal sehen.</t>
         </is>
       </c>
     </row>
@@ -14911,7 +16076,6 @@
           <t>Eat where the locals eat to find the best food.</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr">
         <is>
           <t>B1</t>
@@ -14922,10 +16086,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>Die Einheimischen waren freundlich und gaben uns gute Tipps.</t>
         </is>
       </c>
     </row>
@@ -14965,7 +16133,6 @@
           <t>A detour added an hour to our journey.</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr">
         <is>
           <t>B2</t>
@@ -14976,10 +16143,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>Wir machten einen kurzen Umweg, um den Wasserfall zu sehen.</t>
         </is>
       </c>
     </row>
@@ -15019,7 +16190,6 @@
           <t>For me, the highlight was the old market square.</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr">
         <is>
           <t>B1</t>
@@ -15030,10 +16200,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>Die Bootsfahrt war der Höhepunkt unseres Urlaubs.</t>
         </is>
       </c>
     </row>
@@ -15073,7 +16247,6 @@
           <t>Let's explore the coast before the rain comes.</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr">
         <is>
           <t>B1</t>
@@ -15084,10 +16257,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>Wir verbrachten den Nachmittag damit, die engen Gassen zu erkunden.</t>
         </is>
       </c>
     </row>
@@ -15127,7 +16304,6 @@
           <t>The hotel offers excursions to the mountains.</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr">
         <is>
           <t>B1</t>
@@ -15138,10 +16314,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>Wir buchten einen Tagesausflug zu den nahe gelegenen Inseln.</t>
         </is>
       </c>
     </row>
@@ -15181,7 +16361,6 @@
           <t>This site is protected as a world heritage location.</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr">
         <is>
           <t>B2</t>
@@ -15192,10 +16371,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>Die Altstadt ist Teil des Kulturerbes des Landes.</t>
         </is>
       </c>
     </row>
@@ -15235,7 +16418,6 @@
           <t>Most attractions are within walking distance.</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr">
         <is>
           <t>B1</t>
@@ -15246,10 +16428,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>Das Schloss ist die Hauptsehenswürdigkeit der Stadt.</t>
         </is>
       </c>
     </row>
@@ -15289,7 +16475,6 @@
           <t>The summer festival attracts visitors from all over.</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr">
         <is>
           <t>A2</t>
@@ -15300,10 +16485,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>Wir kamen während eines bunten Straßenfests an.</t>
         </is>
       </c>
     </row>
@@ -15343,7 +16532,6 @@
           <t>I packed a high-factor sunscreen for the trip.</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr">
         <is>
           <t>B1</t>
@@ -15354,10 +16542,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>Vergiss nicht, am Strand Sonnencreme aufzutragen.</t>
         </is>
       </c>
     </row>
@@ -15397,7 +16589,6 @@
           <t>Cover up to avoid sunburn around noon.</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr">
         <is>
           <t>B1</t>
@@ -15408,10 +16599,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>Er bekam am ersten Tag einen schmerzhaften Sonnenbrand.</t>
         </is>
       </c>
     </row>
@@ -15451,7 +16646,6 @@
           <t>She bought a new swimsuit for the holiday.</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr">
         <is>
           <t>B1</t>
@@ -15462,10 +16656,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>Pack deinen Badeanzug ein – das Hotel hat einen Pool.</t>
         </is>
       </c>
     </row>
@@ -15505,7 +16703,6 @@
           <t>I don't like to sunbathe for too long.</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr">
         <is>
           <t>B1</t>
@@ -15516,10 +16713,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>Sie verbrachten den Nachmittag damit, am Meer zu sonnenbaden.</t>
         </is>
       </c>
     </row>
@@ -15559,7 +16760,6 @@
           <t>The pharmacy gave me something for my headache.</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr">
         <is>
           <t>B1</t>
@@ -15570,10 +16770,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>Gibt es eine Apotheke in der Nähe des Hotels?</t>
         </is>
       </c>
     </row>
@@ -15613,7 +16817,6 @@
           <t>The insurance covered the cost of the lost luggage.</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr">
         <is>
           <t>B2</t>
@@ -15624,10 +16827,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>Stelle sicher, dass du eine Reiseversicherung hast, bevor du fährst.</t>
         </is>
       </c>
     </row>
@@ -15667,7 +16874,6 @@
           <t>The hotel has a doctor on call for emergencies.</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr">
         <is>
           <t>B1</t>
@@ -15678,10 +16884,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>Rufen Sie im Notfall diese Nummer an, um Hilfe zu erhalten.</t>
         </is>
       </c>
     </row>
@@ -15721,7 +16931,6 @@
           <t>She found her camera at the station's lost and found.</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr">
         <is>
           <t>B2</t>
@@ -15732,10 +16941,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>Ich fragte im Fundbüro nach meinem Regenschirm.</t>
         </is>
       </c>
     </row>
@@ -15775,7 +16988,6 @@
           <t>We asked a local for directions to the museum.</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr">
         <is>
           <t>B1</t>
@@ -15786,10 +16998,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>Könnten Sie mir den Weg zum alten Hafen beschreiben?</t>
         </is>
       </c>
     </row>
@@ -15829,7 +17045,6 @@
           <t>We got lost twice before finding the restaurant.</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr">
         <is>
           <t>B1</t>
@@ -15840,10 +17055,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>In diesen engen Gassen verirrt man sich leicht.</t>
         </is>
       </c>
     </row>
@@ -15883,7 +17102,6 @@
           <t>We found a lovely café nearby for breakfast.</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr">
         <is>
           <t>A2</t>
@@ -15894,10 +17112,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
       <c r="L283" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>Gibt es einen Supermarkt in der Nähe?</t>
         </is>
       </c>
     </row>
@@ -15937,7 +17159,6 @@
           <t>We avoided the crowded main square at midday.</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr">
         <is>
           <t>B1</t>
@@ -15948,10 +17169,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>Der Strand war zu überfüllt, um einen freien Platz zu finden.</t>
         </is>
       </c>
     </row>
@@ -15991,7 +17216,6 @@
           <t>The set menu is tasty and affordable.</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr">
         <is>
           <t>B1</t>
@@ -16002,10 +17226,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>Wir fanden ein erschwingliches Hotel in der Nähe des Zentrums.</t>
         </is>
       </c>
     </row>
@@ -16045,7 +17273,6 @@
           <t>We watched a stunning sunset over the bay.</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr">
         <is>
           <t>B1</t>
@@ -16056,10 +17283,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>Die Aussicht von der Klippe war absolut atemberaubend.</t>
         </is>
       </c>
     </row>
@@ -16099,7 +17330,6 @@
           <t>He haggled with the seller and saved ten euros.</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr">
         <is>
           <t>B2</t>
@@ -16110,10 +17340,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>Auf dem Markt wird erwartet, dass man ein wenig feilscht.</t>
         </is>
       </c>
     </row>
@@ -16153,7 +17387,6 @@
           <t>The airline offered a full refund for the delay.</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr">
         <is>
           <t>B1</t>
@@ -16164,10 +17397,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Wir baten um eine Rückerstattung, als die Tour abgesagt wurde.</t>
         </is>
       </c>
     </row>
@@ -16207,7 +17444,6 @@
           <t>I'd recommend visiting the market early in the morning.</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr">
         <is>
           <t>B1</t>
@@ -16218,10 +17454,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>Können Sie einen guten Ort zum Abendessen empfehlen?</t>
         </is>
       </c>
     </row>
@@ -16261,7 +17501,6 @@
           <t>Did you pack the charger and the adapter?</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr">
         <is>
           <t>A2</t>
@@ -16272,10 +17511,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Ich packe immer leicht, wenn ich mit dem Flugzeug reise.</t>
         </is>
       </c>
     </row>
@@ -16315,7 +17558,6 @@
           <t>I forgot my adapter and couldn't charge my laptop.</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr">
         <is>
           <t>B1</t>
@@ -16326,10 +17568,14 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr">
         <is>
           <t>Reisen</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>Bring einen Reiseadapter für dein Handyladegerät mit.</t>
         </is>
       </c>
     </row>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vokabeln" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fortschritt" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Vokabeln" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fortschritt" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M291"/>
+  <dimension ref="A1:M292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17576,6 +17576,63 @@
       <c r="M291" t="inlineStr">
         <is>
           <t>Bring einen Reiseadapter für dein Handyladegerät mit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>to indulge</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>sich hingeben</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>/ɪnˈdʌldʒ/</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>To allow oneself to enjoy something pleasurable, especially excessively.</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>I like to indulge in chocolate cake on weekends.</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Parents should not indulge their children's every whim.</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="n">
+        <v>2</v>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>Ich gebe mich am Wochenende gerne Schokoladenkuchen hin.</t>
         </is>
       </c>
     </row>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M292"/>
+  <dimension ref="A1:M293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17615,7 +17615,6 @@
           <t>Parents should not indulge their children's every whim.</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr"/>
       <c r="I292" t="n">
         <v>2</v>
       </c>
@@ -17624,7 +17623,6 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -17633,6 +17631,67 @@
       <c r="M292" t="inlineStr">
         <is>
           <t>Ich gebe mich am Wochenende gerne Schokoladenkuchen hin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Physiotherapist</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Physiotherapeut</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>/ˌfɪziəʊˈθerəpɪst/</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>A healthcare professional who treats injuries and movement problems through physical methods like exercise and massage.</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>The physiotherapist helped me recover from my knee injury.</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>She works as a physiotherapist at the local hospital.</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/8/8c/Physical_Therapists_at_work.jpg</t>
+        </is>
+      </c>
+      <c r="I293" t="n">
+        <v>2</v>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>Der Physiotherapeut half mir, mich von meiner Knieverletzung zu erholen.</t>
         </is>
       </c>
     </row>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M293"/>
+  <dimension ref="A1:M294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17683,7 +17683,6 @@
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -17692,6 +17691,63 @@
       <c r="M293" t="inlineStr">
         <is>
           <t>Der Physiotherapeut half mir, mich von meiner Knieverletzung zu erholen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>no casualties</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>keine Opfer</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>/nəʊ ˈkæʒuəltiz/</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Phrase</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>No people were killed or injured in an incident or accident.</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>The building collapsed, but fortunately there were no casualties.</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>The fire was quickly extinguished with no casualties reported.</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="n">
+        <v>2</v>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>Das Gebäude stürzte ein, aber glücklicherweise gab es keine Opfer.</t>
         </is>
       </c>
     </row>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M294"/>
+  <dimension ref="A1:M295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17730,7 +17730,6 @@
           <t>The fire was quickly extinguished with no casualties reported.</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr"/>
       <c r="I294" t="n">
         <v>2</v>
       </c>
@@ -17739,7 +17738,6 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr">
         <is>
           <t>TV</t>
@@ -17748,6 +17746,63 @@
       <c r="M294" t="inlineStr">
         <is>
           <t>Das Gebäude stürzte ein, aber glücklicherweise gab es keine Opfer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Manslaughter</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Totschlag</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>/ˈmænˌslɔːtər/</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>The unlawful killing of a person without intent or premeditation.</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>He was convicted of manslaughter after the accident.</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>The jury had to decide between murder and manslaughter.</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="n">
+        <v>3</v>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>Er wurde nach dem Unfall wegen Totschlags verurteilt.</t>
         </is>
       </c>
     </row>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M295"/>
+  <dimension ref="A1:M296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17785,7 +17785,6 @@
           <t>The jury had to decide between murder and manslaughter.</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr"/>
       <c r="I295" t="n">
         <v>3</v>
       </c>
@@ -17794,7 +17793,6 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
       <c r="L295" t="inlineStr">
         <is>
           <t>TV</t>
@@ -17803,6 +17801,63 @@
       <c r="M295" t="inlineStr">
         <is>
           <t>Er wurde nach dem Unfall wegen Totschlags verurteilt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>to lurk</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>lauern</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>/lɜːrk/</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>To wait hidden, ready to attack or appear suddenly.</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>A cat was lurking in the bushes.</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Someone is lurking outside our house.</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="n">
+        <v>2</v>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>Eine Katze lauerte in den Büschen.</t>
         </is>
       </c>
     </row>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M296"/>
+  <dimension ref="A1:M297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17840,7 +17840,6 @@
           <t>Someone is lurking outside our house.</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr"/>
       <c r="I296" t="n">
         <v>2</v>
       </c>
@@ -17849,7 +17848,6 @@
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr">
         <is>
           <t>Allgemein</t>
@@ -17858,6 +17856,63 @@
       <c r="M296" t="inlineStr">
         <is>
           <t>Eine Katze lauerte in den Büschen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Wholesome</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>gesund, heilsam</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>/ˈhoʊlsəm/</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Adjektiv</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Good for your health or character; morally beneficial and pure.</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>She enjoys wholesome food like fresh vegetables and fruit.</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>The movie is wholesome entertainment for the whole family.</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="n">
+        <v>2</v>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>Sie genießt gesunde Nahrung wie frisches Gemüse und Obst.</t>
         </is>
       </c>
     </row>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Vokabeln" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Fortschritt" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vokabeln" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fortschritt" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17615,8 +17615,10 @@
           <t>Parents should not indulge their children's every whim.</t>
         </is>
       </c>
-      <c r="I292" t="n">
-        <v>2</v>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
@@ -17675,8 +17677,10 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/8/8c/Physical_Therapists_at_work.jpg</t>
         </is>
       </c>
-      <c r="I293" t="n">
-        <v>2</v>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
@@ -17730,8 +17734,10 @@
           <t>The fire was quickly extinguished with no casualties reported.</t>
         </is>
       </c>
-      <c r="I294" t="n">
-        <v>2</v>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
@@ -17785,8 +17791,10 @@
           <t>The jury had to decide between murder and manslaughter.</t>
         </is>
       </c>
-      <c r="I295" t="n">
-        <v>3</v>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
@@ -17840,8 +17848,10 @@
           <t>Someone is lurking outside our house.</t>
         </is>
       </c>
-      <c r="I296" t="n">
-        <v>2</v>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
@@ -17895,16 +17905,16 @@
           <t>The movie is wholesome entertainment for the whole family.</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr"/>
-      <c r="I297" t="n">
-        <v>2</v>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr">
         <is>
           <t>TV</t>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vokabeln" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fortschritt" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Vokabeln" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fortschritt" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M297"/>
+  <dimension ref="A1:M298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17923,6 +17923,69 @@
       <c r="M297" t="inlineStr">
         <is>
           <t>Sie genießt gesunde Nahrung wie frisches Gemüse und Obst.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Ambush</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Hinterhalt</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>/ˈæmbʊʃ/</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>A surprise attack from a hidden position against an unsuspecting target.</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>The soldiers were caught in an ambush on the mountain road.</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>The rebels set up an ambush near the village entrance.</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/3/38/Embuscade_%28Guerre_de_Vend%C3%A9e%29_-_Evariste_Carpentier_%281%29-.jpg?utm_source=en.wikipedia.org&amp;utm_campaign=api&amp;utm_content=thumbnail_unscaled</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>Die Soldaten gerieten auf der Bergstraße in einen Hinterhalt.</t>
         </is>
       </c>
     </row>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M298"/>
+  <dimension ref="A1:M299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17977,7 +17977,6 @@
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr">
         <is>
           <t>TV</t>
@@ -17986,6 +17985,65 @@
       <c r="M298" t="inlineStr">
         <is>
           <t>Die Soldaten gerieten auf der Bergstraße in einen Hinterhalt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>retrieval mission</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Bergungseinsatz</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>/rɪˈtriːvəl ˈmɪʃən/</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Phrase</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>An operation to recover or bring back something or someone from a location.</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>The team went on a retrieval mission to recover the lost equipment.</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>The astronauts completed a successful retrieval mission in space.</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>Das Team startete einen Bergungseinsatz, um die verlorene Ausrüstung zu bergen.</t>
         </is>
       </c>
     </row>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vokabeln" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Vokabeln" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M296"/>
+  <dimension ref="A1:M297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18424,6 +18424,69 @@
         </is>
       </c>
     </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Taillight</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Rücklicht</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>/ˈteɪllaɪt/</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Nomen</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>A red light at the rear of a vehicle that indicates its presence.</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>The broken taillight made the car unsafe to drive at night.</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Police officers often stop vehicles with missing taillights.</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Reisebus.Heck.jpg/330px-Reisebus.Heck.jpg?utm_source=en.wikipedia.org&amp;utm_campaign=api&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>Das kaputte Rücklicht machte das Auto unsicher für nächtliche Fahrten.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
